--- a/inasistencias-5a-tec-Dig/alumnos-5a-td.xlsx
+++ b/inasistencias-5a-tec-Dig/alumnos-5a-td.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,14 +30,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="320">
   <si>
     <t xml:space="preserve">total</t>
   </si>
   <si>
-    <t xml:space="preserve">Total 9</t>
-  </si>
-  <si>
     <t xml:space="preserve">nro</t>
   </si>
   <si>
@@ -68,12 +65,6 @@
     <t xml:space="preserve">media</t>
   </si>
   <si>
-    <t xml:space="preserve">m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lucila Yanel</t>
   </si>
   <si>
@@ -308,6 +299,12 @@
     <t xml:space="preserve">2do Cuat</t>
   </si>
   <si>
+    <t xml:space="preserve">Nota Diciembre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">observaciones</t>
+  </si>
+  <si>
     <t xml:space="preserve">1-codigo</t>
   </si>
   <si>
@@ -387,6 +384,9 @@
   </si>
   <si>
     <t xml:space="preserve">Recuperacion Agosto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprobo</t>
   </si>
   <si>
     <t xml:space="preserve">Finalizado</t>
@@ -1026,7 +1026,7 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1043,6 +1043,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC107"/>
         <bgColor rgb="FFFF9900"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81D41A"/>
+        <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
     <fill>
@@ -1093,7 +1099,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1110,10 +1116,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1122,11 +1124,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1138,7 +1156,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1146,7 +1164,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1159,7 +1181,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="9">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -1173,7 +1195,6 @@
           <bgColor rgb="FFCCFFCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -1188,7 +1209,6 @@
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -1204,7 +1224,6 @@
           <bgColor rgb="FFCC0000"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -1259,6 +1278,34 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF006600"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FFCC0000"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -1304,7 +1351,7 @@
       <rgbColor rgb="FFFFCCCC"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFC107"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
@@ -1444,8 +1491,7 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="11" min="5" style="1" width="8.68"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="12" min="12" style="1" width="12.64"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="22" min="13" style="1" width="8.68"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="31" min="23" style="1" width="8.75"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="38" min="32" style="0" width="8.75"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="42" min="23" style="1" width="8.75"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1465,34 +1511,28 @@
       <c r="W1" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AR1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="AT1" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU1" s="0" t="n">
-        <v>10</v>
-      </c>
+      <c r="AR1" s="2"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>45800</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>45807</v>
@@ -1501,13 +1541,13 @@
         <v>45814</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>45821</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>45835</v>
@@ -1516,31 +1556,31 @@
         <v>45842</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>45849</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="R2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="T2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W2" s="3" t="n">
         <v>45856</v>
@@ -1549,37 +1589,37 @@
         <v>45898</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z2" s="3" t="n">
         <v>45905</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB2" s="3" t="n">
         <v>45919</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD2" s="3" t="n">
         <v>45926</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF2" s="3" t="n">
         <v>45933</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH2" s="3" t="n">
         <v>45947</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ2" s="3" t="n">
         <v>45954</v>
@@ -1587,63 +1627,62 @@
       <c r="AK2" s="3" t="n">
         <v>45961</v>
       </c>
-      <c r="AL2" s="4" t="s">
+      <c r="AL2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AM2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN2" s="4" t="s">
+      <c r="AN2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ2" s="3" t="n">
+        <v>45996</v>
+      </c>
+      <c r="AT2" s="2"/>
+      <c r="AU2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="AO2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="AP2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="AT2" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AU2" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P3" s="5" t="n">
+      <c r="P3" s="4" t="n">
         <v>0.520833333333333</v>
       </c>
       <c r="Q3" s="1" t="n">
@@ -1662,87 +1701,87 @@
         <f aca="false">ROUND(Q3+R3/2+S3/4,0)</f>
         <v>7</v>
       </c>
-      <c r="V3" s="6" t="n">
+      <c r="V3" s="5" t="n">
         <f aca="false">ROUND(T3*10/$W$1,0)</f>
         <v>10</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AJ3" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AK3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM3" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM3" s="2" t="n">
         <f aca="false">COUNTIF(W3:AL3,"p")</f>
         <v>6</v>
       </c>
-      <c r="AN3" s="4" t="n">
+      <c r="AN3" s="2" t="n">
         <f aca="false">COUNTIF(W3:AL3,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO3" s="4" t="n">
+      <c r="AO3" s="2" t="n">
         <f aca="false">COUNTIF(W3:AL3,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP3" s="7" t="n">
+      <c r="AP3" s="6" t="n">
         <f aca="false">ROUND((AM3+AN3/2+AO3/4)*10/9,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q4" s="1" t="n">
         <f aca="false">COUNTIF(E4:O4,"P")</f>
@@ -1760,89 +1799,89 @@
         <f aca="false">ROUND(Q4+R4/2+S4/4,0)</f>
         <v>7</v>
       </c>
-      <c r="V4" s="6" t="n">
+      <c r="V4" s="5" t="n">
         <f aca="false">ROUND(T4*10/$W$1,0)</f>
         <v>10</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AJ4" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM4" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM4" s="2" t="n">
         <f aca="false">COUNTIF(W4:AL4,"p")</f>
         <v>9</v>
       </c>
-      <c r="AN4" s="4" t="n">
+      <c r="AN4" s="2" t="n">
         <f aca="false">COUNTIF(W4:AL4,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO4" s="4" t="n">
+      <c r="AO4" s="2" t="n">
         <f aca="false">COUNTIF(W4:AL4,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP4" s="7" t="n">
+      <c r="AP4" s="6" t="n">
         <f aca="false">ROUND((AM4+AN4/2+AO4/4)*10/9,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P5" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="P5" s="4" t="n">
         <v>0.520833333333333</v>
       </c>
       <c r="Q5" s="1" t="n">
@@ -1861,89 +1900,89 @@
         <f aca="false">ROUND(Q5+R5/2+S5/4,0)</f>
         <v>7</v>
       </c>
-      <c r="V5" s="6" t="n">
+      <c r="V5" s="5" t="n">
         <f aca="false">ROUND(T5*10/$W$1,0)</f>
         <v>10</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AD5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AF5" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AK5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM5" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM5" s="2" t="n">
         <f aca="false">COUNTIF(W5:AL5,"p")</f>
         <v>6</v>
       </c>
-      <c r="AN5" s="4" t="n">
+      <c r="AN5" s="2" t="n">
         <f aca="false">COUNTIF(W5:AL5,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO5" s="4" t="n">
+      <c r="AO5" s="2" t="n">
         <f aca="false">COUNTIF(W5:AL5,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP5" s="7" t="n">
+      <c r="AP5" s="6" t="n">
         <f aca="false">ROUND((AM5+AN5/2+AO5/4)*10/9,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P6" s="5" t="n">
+      <c r="P6" s="4" t="n">
         <v>0.53125</v>
       </c>
       <c r="Q6" s="1" t="n">
@@ -1962,95 +2001,95 @@
         <f aca="false">ROUND(Q6+R6/2+S6/4,0)</f>
         <v>3</v>
       </c>
-      <c r="V6" s="6" t="n">
+      <c r="V6" s="5" t="n">
         <f aca="false">ROUND(T6*10/$W$1,0)</f>
         <v>4</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AF6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AJ6" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AK6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM6" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM6" s="2" t="n">
         <f aca="false">COUNTIF(W6:AL6,"p")</f>
         <v>7</v>
       </c>
-      <c r="AN6" s="4" t="n">
+      <c r="AN6" s="2" t="n">
         <f aca="false">COUNTIF(W6:AL6,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO6" s="4" t="n">
+      <c r="AO6" s="2" t="n">
         <f aca="false">COUNTIF(W6:AL6,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP6" s="7" t="n">
+      <c r="AP6" s="6" t="n">
         <f aca="false">ROUND((AM6+AN6/2+AO6/4)*10/9,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>0.555555555555555</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>0.527777777777778</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P7" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="P7" s="4" t="n">
         <v>0.548611111111111</v>
       </c>
       <c r="Q7" s="1" t="n">
@@ -2069,200 +2108,214 @@
         <f aca="false">ROUND(Q7+R7/2+S7/4,0)</f>
         <v>3</v>
       </c>
-      <c r="V7" s="6" t="n">
+      <c r="V7" s="5" t="n">
         <f aca="false">ROUND(T7*10/$W$1,0)</f>
         <v>4</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y7" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y7" s="4" t="n">
         <v>0.532638888888889</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE7" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE7" s="4" t="n">
         <v>0.572916666666667</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AJ7" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AK7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM7" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AM7" s="2" t="n">
         <f aca="false">COUNTIF(W7:AL7,"p")</f>
         <v>3</v>
       </c>
-      <c r="AN7" s="4" t="n">
+      <c r="AN7" s="2" t="n">
         <f aca="false">COUNTIF(W7:AL7,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO7" s="4" t="n">
+      <c r="AO7" s="2" t="n">
         <f aca="false">COUNTIF(W7:AL7,"T")</f>
         <v>2</v>
       </c>
-      <c r="AP7" s="7" t="n">
+      <c r="AP7" s="6" t="n">
         <f aca="false">ROUND((AM7+AN7/2+AO7/4)*10/9,0)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+    <row r="8" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q8" s="1" t="n">
+      <c r="B8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7" t="n">
         <f aca="false">COUNTIF(E8:O8,"P")</f>
         <v>7</v>
       </c>
-      <c r="R8" s="1" t="n">
+      <c r="R8" s="7" t="n">
         <f aca="false">COUNTIF(E8:O8,"M")</f>
         <v>0</v>
       </c>
-      <c r="S8" s="1" t="n">
+      <c r="S8" s="7" t="n">
         <f aca="false">COUNTIF(E8:O8,"T")</f>
         <v>0</v>
       </c>
-      <c r="T8" s="1" t="n">
+      <c r="T8" s="7" t="n">
         <f aca="false">ROUND(Q8+R8/2+S8/4,0)</f>
         <v>7</v>
       </c>
-      <c r="V8" s="6" t="n">
+      <c r="U8" s="7"/>
+      <c r="V8" s="9" t="n">
         <f aca="false">ROUND(T8*10/$W$1,0)</f>
         <v>10</v>
       </c>
-      <c r="W8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA8" s="5" t="n">
+      <c r="W8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="X8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA8" s="10" t="n">
         <v>0.517361111111111</v>
       </c>
-      <c r="AB8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE8" s="5" t="n">
+      <c r="AB8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE8" s="10" t="n">
         <v>0.520833333333333</v>
       </c>
-      <c r="AF8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AK8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM8" s="4" t="n">
+      <c r="AF8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG8" s="7"/>
+      <c r="AH8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI8" s="7"/>
+      <c r="AJ8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL8" s="7"/>
+      <c r="AM8" s="8" t="n">
         <f aca="false">COUNTIF(W8:AL8,"p")</f>
         <v>4</v>
       </c>
-      <c r="AN8" s="4" t="n">
+      <c r="AN8" s="8" t="n">
         <f aca="false">COUNTIF(W8:AL8,"M")</f>
         <v>1</v>
       </c>
-      <c r="AO8" s="4" t="n">
+      <c r="AO8" s="8" t="n">
         <f aca="false">COUNTIF(W8:AL8,"T")</f>
         <v>1</v>
       </c>
-      <c r="AP8" s="7" t="n">
+      <c r="AP8" s="11" t="n">
         <f aca="false">ROUND((AM8+AN8/2+AO8/4)*10/9,0)</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AQ8" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N9" s="4" t="n">
         <v>0.520833333333333</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q9" s="1" t="n">
         <f aca="false">COUNTIF(E9:O9,"P")</f>
@@ -2280,90 +2333,90 @@
         <f aca="false">ROUND(Q9+R9/2+S9/4,0)</f>
         <v>7</v>
       </c>
-      <c r="V9" s="6" t="n">
+      <c r="V9" s="5" t="n">
         <f aca="false">ROUND(T9*10/$W$1,0)</f>
         <v>10</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM9" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM9" s="2" t="n">
         <f aca="false">COUNTIF(W9:AL9,"p")</f>
         <v>8</v>
       </c>
-      <c r="AN9" s="4" t="n">
+      <c r="AN9" s="2" t="n">
         <f aca="false">COUNTIF(W9:AL9,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO9" s="4" t="n">
+      <c r="AO9" s="2" t="n">
         <f aca="false">COUNTIF(W9:AL9,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP9" s="7" t="n">
+      <c r="AP9" s="6" t="n">
         <f aca="false">ROUND((AM9+AN9/2+AO9/4)*10/9,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="J10" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q10" s="1" t="n">
         <f aca="false">COUNTIF(E10:O10,"P")</f>
@@ -2381,90 +2434,90 @@
         <f aca="false">ROUND(Q10+R10/2+S10/4,0)</f>
         <v>7</v>
       </c>
-      <c r="V10" s="6" t="n">
+      <c r="V10" s="5" t="n">
         <f aca="false">ROUND(T10*10/$W$1,0)</f>
         <v>10</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AD10" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AJ10" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM10" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM10" s="2" t="n">
         <f aca="false">COUNTIF(W10:AL10,"p")</f>
         <v>8</v>
       </c>
-      <c r="AN10" s="4" t="n">
+      <c r="AN10" s="2" t="n">
         <f aca="false">COUNTIF(W10:AL10,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO10" s="4" t="n">
+      <c r="AO10" s="2" t="n">
         <f aca="false">COUNTIF(W10:AL10,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP10" s="7" t="n">
+      <c r="AP10" s="6" t="n">
         <f aca="false">ROUND((AM10+AN10/2+AO10/4)*10/9,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q11" s="1" t="n">
         <f aca="false">COUNTIF(E11:O11,"P")</f>
@@ -2482,188 +2535,204 @@
         <f aca="false">ROUND(Q11+R11/2+S11/4,0)</f>
         <v>7</v>
       </c>
-      <c r="V11" s="6" t="n">
+      <c r="V11" s="5" t="n">
         <f aca="false">ROUND(T11*10/$W$1,0)</f>
         <v>10</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AF11" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AJ11" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AK11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM11" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AM11" s="2" t="n">
         <f aca="false">COUNTIF(W11:AL11,"p")</f>
         <v>4</v>
       </c>
-      <c r="AN11" s="4" t="n">
+      <c r="AN11" s="2" t="n">
         <f aca="false">COUNTIF(W11:AL11,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO11" s="4" t="n">
+      <c r="AO11" s="2" t="n">
         <f aca="false">COUNTIF(W11:AL11,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP11" s="7" t="n">
+      <c r="AP11" s="6" t="n">
         <f aca="false">ROUND((AM11+AN11/2+AO11/4)*10/9,0)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q12" s="1" t="n">
+    <row r="12" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7" t="n">
         <f aca="false">COUNTIF(E12:O12,"P")</f>
         <v>7</v>
       </c>
-      <c r="R12" s="1" t="n">
+      <c r="R12" s="7" t="n">
         <f aca="false">COUNTIF(E12:O12,"M")</f>
         <v>0</v>
       </c>
-      <c r="S12" s="1" t="n">
+      <c r="S12" s="7" t="n">
         <f aca="false">COUNTIF(E12:O12,"T")</f>
         <v>0</v>
       </c>
-      <c r="T12" s="1" t="n">
+      <c r="T12" s="7" t="n">
         <f aca="false">ROUND(Q12+R12/2+S12/4,0)</f>
         <v>7</v>
       </c>
-      <c r="V12" s="6" t="n">
+      <c r="U12" s="7"/>
+      <c r="V12" s="9" t="n">
         <f aca="false">ROUND(T12*10/$W$1,0)</f>
         <v>10</v>
       </c>
-      <c r="W12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="X12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM12" s="4" t="n">
+      <c r="W12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="X12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC12" s="7"/>
+      <c r="AD12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE12" s="7"/>
+      <c r="AF12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG12" s="7"/>
+      <c r="AH12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI12" s="7"/>
+      <c r="AJ12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL12" s="7"/>
+      <c r="AM12" s="8" t="n">
         <f aca="false">COUNTIF(W12:AL12,"p")</f>
         <v>6</v>
       </c>
-      <c r="AN12" s="4" t="n">
+      <c r="AN12" s="8" t="n">
         <f aca="false">COUNTIF(W12:AL12,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO12" s="4" t="n">
+      <c r="AO12" s="8" t="n">
         <f aca="false">COUNTIF(W12:AL12,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP12" s="7" t="n">
+      <c r="AP12" s="11" t="n">
         <f aca="false">ROUND((AM12+AN12/2+AO12/4)*10/9,0)</f>
         <v>7</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AQ12" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q13" s="1" t="n">
         <f aca="false">COUNTIF(E13:O13,"P")</f>
@@ -2681,93 +2750,93 @@
         <f aca="false">ROUND(Q13+R13/2+S13/4,0)</f>
         <v>7</v>
       </c>
-      <c r="V13" s="6" t="n">
+      <c r="V13" s="5" t="n">
         <f aca="false">ROUND(T13*10/$W$1,0)</f>
         <v>10</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE13" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE13" s="4" t="n">
         <v>0.520833333333333</v>
       </c>
       <c r="AF13" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AJ13" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AK13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM13" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM13" s="2" t="n">
         <f aca="false">COUNTIF(W13:AL13,"p")</f>
         <v>7</v>
       </c>
-      <c r="AN13" s="4" t="n">
+      <c r="AN13" s="2" t="n">
         <f aca="false">COUNTIF(W13:AL13,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO13" s="4" t="n">
+      <c r="AO13" s="2" t="n">
         <f aca="false">COUNTIF(W13:AL13,"T")</f>
         <v>1</v>
       </c>
-      <c r="AP13" s="7" t="n">
+      <c r="AP13" s="6" t="n">
         <f aca="false">ROUND((AM13+AN13/2+AO13/4)*10/9,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q14" s="1" t="n">
         <f aca="false">COUNTIF(E14:O14,"P")</f>
@@ -2785,185 +2854,201 @@
         <f aca="false">ROUND(Q14+R14/2+S14/4,0)</f>
         <v>6</v>
       </c>
-      <c r="V14" s="6" t="n">
+      <c r="V14" s="5" t="n">
         <f aca="false">ROUND(T14*10/$W$1,0)</f>
         <v>9</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AD14" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AF14" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AJ14" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AK14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM14" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM14" s="2" t="n">
         <f aca="false">COUNTIF(W14:AL14,"p")</f>
         <v>6</v>
       </c>
-      <c r="AN14" s="4" t="n">
+      <c r="AN14" s="2" t="n">
         <f aca="false">COUNTIF(W14:AL14,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO14" s="4" t="n">
+      <c r="AO14" s="2" t="n">
         <f aca="false">COUNTIF(W14:AL14,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP14" s="7" t="n">
+      <c r="AP14" s="6" t="n">
         <f aca="false">ROUND((AM14+AN14/2+AO14/4)*10/9,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
+    <row r="15" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q15" s="1" t="n">
+      <c r="B15" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7" t="n">
         <f aca="false">COUNTIF(E15:O15,"P")</f>
         <v>6</v>
       </c>
-      <c r="R15" s="1" t="n">
+      <c r="R15" s="7" t="n">
         <f aca="false">COUNTIF(E15:O15,"M")</f>
         <v>0</v>
       </c>
-      <c r="S15" s="1" t="n">
+      <c r="S15" s="7" t="n">
         <f aca="false">COUNTIF(E15:O15,"T")</f>
         <v>0</v>
       </c>
-      <c r="T15" s="1" t="n">
+      <c r="T15" s="7" t="n">
         <f aca="false">ROUND(Q15+R15/2+S15/4,0)</f>
         <v>6</v>
       </c>
-      <c r="V15" s="6" t="n">
+      <c r="U15" s="7"/>
+      <c r="V15" s="9" t="n">
         <f aca="false">ROUND(T15*10/$W$1,0)</f>
         <v>9</v>
       </c>
-      <c r="W15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="X15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AK15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM15" s="4" t="n">
+      <c r="W15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="X15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC15" s="7"/>
+      <c r="AD15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE15" s="7"/>
+      <c r="AF15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG15" s="7"/>
+      <c r="AH15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI15" s="7"/>
+      <c r="AJ15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL15" s="7"/>
+      <c r="AM15" s="8" t="n">
         <f aca="false">COUNTIF(W15:AL15,"p")</f>
         <v>8</v>
       </c>
-      <c r="AN15" s="4" t="n">
+      <c r="AN15" s="8" t="n">
         <f aca="false">COUNTIF(W15:AL15,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO15" s="4" t="n">
+      <c r="AO15" s="8" t="n">
         <f aca="false">COUNTIF(W15:AL15,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP15" s="7" t="n">
+      <c r="AP15" s="11" t="n">
         <f aca="false">ROUND((AM15+AN15/2+AO15/4)*10/9,0)</f>
         <v>9</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AQ15" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q16" s="1" t="n">
         <f aca="false">COUNTIF(E16:O16,"P")</f>
@@ -2981,87 +3066,87 @@
         <f aca="false">ROUND(Q16+R16/2+S16/4,0)</f>
         <v>5</v>
       </c>
-      <c r="V16" s="6" t="n">
+      <c r="V16" s="5" t="n">
         <f aca="false">ROUND(T16*10/$W$1,0)</f>
         <v>7</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AD16" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AJ16" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AK16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM16" s="2" t="n">
         <f aca="false">COUNTIF(W16:AL16,"p")</f>
         <v>9</v>
       </c>
-      <c r="AN16" s="4" t="n">
+      <c r="AN16" s="2" t="n">
         <f aca="false">COUNTIF(W16:AL16,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO16" s="4" t="n">
+      <c r="AO16" s="2" t="n">
         <f aca="false">COUNTIF(W16:AL16,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP16" s="7" t="n">
+      <c r="AP16" s="6" t="n">
         <f aca="false">ROUND((AM16+AN16/2+AO16/4)*10/9,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="1" t="n">
         <f aca="false">COUNTIF(E17:O17,"P")</f>
@@ -3079,393 +3164,440 @@
         <f aca="false">ROUND(Q17+R17/2+S17/4,0)</f>
         <v>7</v>
       </c>
-      <c r="V17" s="6" t="n">
+      <c r="V17" s="5" t="n">
         <f aca="false">ROUND(T17*10/$W$1,0)</f>
         <v>10</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AD17" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AF17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AJ17" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AK17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AM17" s="2" t="n">
         <f aca="false">COUNTIF(W17:AL17,"p")</f>
         <v>6</v>
       </c>
-      <c r="AN17" s="4" t="n">
+      <c r="AN17" s="2" t="n">
         <f aca="false">COUNTIF(W17:AL17,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO17" s="4" t="n">
+      <c r="AO17" s="2" t="n">
         <f aca="false">COUNTIF(W17:AL17,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP17" s="7" t="n">
+      <c r="AP17" s="6" t="n">
         <f aca="false">ROUND((AM17+AN17/2+AO17/4)*10/9,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
+    <row r="18" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K18" s="5" t="n">
+      <c r="B18" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="10" t="n">
         <v>0.541666666666667</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q18" s="1" t="n">
+      <c r="L18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7" t="n">
         <f aca="false">COUNTIF(E18:O18,"P")</f>
         <v>5</v>
       </c>
-      <c r="R18" s="1" t="n">
+      <c r="R18" s="7" t="n">
         <f aca="false">COUNTIF(E18:O18,"M")</f>
         <v>0</v>
       </c>
-      <c r="S18" s="1" t="n">
+      <c r="S18" s="7" t="n">
         <f aca="false">COUNTIF(E18:O18,"T")</f>
         <v>1</v>
       </c>
-      <c r="T18" s="1" t="n">
+      <c r="T18" s="7" t="n">
         <f aca="false">ROUND(Q18+R18/2+S18/4,0)</f>
         <v>5</v>
       </c>
-      <c r="V18" s="6" t="n">
+      <c r="U18" s="7"/>
+      <c r="V18" s="9" t="n">
         <f aca="false">ROUND(T18*10/$W$1,0)</f>
         <v>7</v>
       </c>
-      <c r="W18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="X18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE18" s="5" t="n">
+      <c r="W18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="X18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA18" s="7"/>
+      <c r="AB18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC18" s="7"/>
+      <c r="AD18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE18" s="10" t="n">
         <v>0.520833333333333</v>
       </c>
-      <c r="AF18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AG18" s="5" t="n">
+      <c r="AF18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG18" s="10" t="n">
         <v>0.545138888888889</v>
       </c>
-      <c r="AH18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AJ18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM18" s="4" t="n">
+      <c r="AH18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI18" s="7"/>
+      <c r="AJ18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL18" s="7"/>
+      <c r="AM18" s="8" t="n">
         <f aca="false">COUNTIF(W18:AL18,"p")</f>
         <v>1</v>
       </c>
-      <c r="AN18" s="4" t="n">
+      <c r="AN18" s="8" t="n">
         <f aca="false">COUNTIF(W18:AL18,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO18" s="4" t="n">
+      <c r="AO18" s="8" t="n">
         <f aca="false">COUNTIF(W18:AL18,"T")</f>
         <v>2</v>
       </c>
-      <c r="AP18" s="7" t="n">
+      <c r="AP18" s="11" t="n">
         <f aca="false">ROUND((AM18+AN18/2+AO18/4)*10/9,0)</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
+      <c r="AQ18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="AR18" s="10" t="n">
+        <v>0.583333333333333</v>
+      </c>
+    </row>
+    <row r="19" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q19" s="1" t="n">
+      <c r="B19" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7" t="n">
         <f aca="false">COUNTIF(E19:O19,"P")</f>
         <v>6</v>
       </c>
-      <c r="R19" s="1" t="n">
+      <c r="R19" s="7" t="n">
         <f aca="false">COUNTIF(E19:O19,"M")</f>
         <v>0</v>
       </c>
-      <c r="S19" s="1" t="n">
+      <c r="S19" s="7" t="n">
         <f aca="false">COUNTIF(E19:O19,"T")</f>
         <v>0</v>
       </c>
-      <c r="T19" s="1" t="n">
+      <c r="T19" s="7" t="n">
         <f aca="false">ROUND(Q19+R19/2+S19/4,0)</f>
         <v>6</v>
       </c>
-      <c r="V19" s="6" t="n">
+      <c r="U19" s="7"/>
+      <c r="V19" s="9" t="n">
         <f aca="false">ROUND(T19*10/$W$1,0)</f>
         <v>9</v>
       </c>
-      <c r="W19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="X19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM19" s="4" t="n">
+      <c r="W19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="X19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA19" s="7"/>
+      <c r="AB19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC19" s="7"/>
+      <c r="AD19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE19" s="7"/>
+      <c r="AF19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG19" s="7"/>
+      <c r="AH19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI19" s="7"/>
+      <c r="AJ19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL19" s="7"/>
+      <c r="AM19" s="8" t="n">
         <f aca="false">COUNTIF(W19:AL19,"p")</f>
         <v>6</v>
       </c>
-      <c r="AN19" s="4" t="n">
+      <c r="AN19" s="8" t="n">
         <f aca="false">COUNTIF(W19:AL19,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO19" s="4" t="n">
+      <c r="AO19" s="8" t="n">
         <f aca="false">COUNTIF(W19:AL19,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP19" s="7" t="n">
+      <c r="AP19" s="11" t="n">
         <f aca="false">ROUND((AM19+AN19/2+AO19/4)*10/9,0)</f>
         <v>7</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
+      <c r="AQ19" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I20" s="5" t="n">
+      <c r="B20" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" s="10" t="n">
         <v>0.527777777777778</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q20" s="1" t="n">
+      <c r="J20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7" t="n">
         <f aca="false">COUNTIF(E20:O20,"P")</f>
         <v>4</v>
       </c>
-      <c r="R20" s="1" t="n">
+      <c r="R20" s="7" t="n">
         <f aca="false">COUNTIF(E20:O20,"M")</f>
         <v>0</v>
       </c>
-      <c r="S20" s="1" t="n">
+      <c r="S20" s="7" t="n">
         <f aca="false">COUNTIF(E20:O20,"T")</f>
         <v>1</v>
       </c>
-      <c r="T20" s="1" t="n">
+      <c r="T20" s="7" t="n">
         <f aca="false">ROUND(Q20+R20/2+S20/4,0)</f>
         <v>4</v>
       </c>
-      <c r="V20" s="6" t="n">
+      <c r="U20" s="7"/>
+      <c r="V20" s="9" t="n">
         <f aca="false">ROUND(T20*10/$W$1,0)</f>
         <v>6</v>
       </c>
-      <c r="W20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="X20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AK20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM20" s="4" t="n">
+      <c r="W20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="X20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y20" s="7"/>
+      <c r="Z20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA20" s="7"/>
+      <c r="AB20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC20" s="7"/>
+      <c r="AD20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE20" s="7"/>
+      <c r="AF20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG20" s="7"/>
+      <c r="AH20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI20" s="7"/>
+      <c r="AJ20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL20" s="7"/>
+      <c r="AM20" s="8" t="n">
         <f aca="false">COUNTIF(W20:AL20,"p")</f>
         <v>6</v>
       </c>
-      <c r="AN20" s="4" t="n">
+      <c r="AN20" s="8" t="n">
         <f aca="false">COUNTIF(W20:AL20,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO20" s="4" t="n">
+      <c r="AO20" s="8" t="n">
         <f aca="false">COUNTIF(W20:AL20,"T")</f>
         <v>1</v>
       </c>
-      <c r="AP20" s="7" t="n">
+      <c r="AP20" s="11" t="n">
         <f aca="false">ROUND((AM20+AN20/2+AO20/4)*10/9,0)</f>
         <v>7</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AQ20" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q21" s="1" t="n">
         <f aca="false">COUNTIF(E21:O21,"P")</f>
@@ -3483,87 +3615,87 @@
         <f aca="false">ROUND(Q21+R21/2+S21/4,0)</f>
         <v>6</v>
       </c>
-      <c r="V21" s="6" t="n">
+      <c r="V21" s="5" t="n">
         <f aca="false">ROUND(T21*10/$W$1,0)</f>
         <v>9</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AD21" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AF21" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AJ21" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AK21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM21" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM21" s="2" t="n">
         <f aca="false">COUNTIF(W21:AL21,"p")</f>
         <v>0</v>
       </c>
-      <c r="AN21" s="4" t="n">
+      <c r="AN21" s="2" t="n">
         <f aca="false">COUNTIF(W21:AL21,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO21" s="4" t="n">
+      <c r="AO21" s="2" t="n">
         <f aca="false">COUNTIF(W21:AL21,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP21" s="7" t="n">
+      <c r="AP21" s="6" t="n">
         <f aca="false">ROUND((AM21+AN21/2+AO21/4)*10/9,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q22" s="1" t="n">
         <f aca="false">COUNTIF(E22:O22,"P")</f>
@@ -3581,95 +3713,95 @@
         <f aca="false">ROUND(Q22+R22/2+S22/4,0)</f>
         <v>7</v>
       </c>
-      <c r="V22" s="6" t="n">
+      <c r="V22" s="5" t="n">
         <f aca="false">ROUND(T22*10/$W$1,0)</f>
         <v>10</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AF22" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AH22" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AJ22" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AK22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM22" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM22" s="2" t="n">
         <f aca="false">COUNTIF(W22:AL22,"p")</f>
         <v>6</v>
       </c>
-      <c r="AN22" s="4" t="n">
+      <c r="AN22" s="2" t="n">
         <f aca="false">COUNTIF(W22:AL22,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO22" s="4" t="n">
+      <c r="AO22" s="2" t="n">
         <f aca="false">COUNTIF(W22:AL22,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP22" s="7" t="n">
+      <c r="AP22" s="6" t="n">
         <f aca="false">ROUND((AM22+AN22/2+AO22/4)*10/9,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N23" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N23" s="4" t="n">
         <v>0.520833333333333</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P23" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="P23" s="4" t="n">
         <v>0.520833333333333</v>
       </c>
       <c r="Q23" s="1" t="n">
@@ -3688,167 +3820,182 @@
         <f aca="false">ROUND(Q23+R23/2+S23/4,0)</f>
         <v>4</v>
       </c>
-      <c r="V23" s="6" t="n">
+      <c r="V23" s="5" t="n">
         <f aca="false">ROUND(T23*10/$W$1,0)</f>
         <v>6</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA23" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA23" s="4" t="n">
         <v>0.517361111111111</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AD23" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AF23" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AJ23" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AK23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AL23" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL23" s="4" t="n">
         <v>0.53125</v>
       </c>
-      <c r="AM23" s="4" t="n">
+      <c r="AM23" s="2" t="n">
         <f aca="false">COUNTIF(W23:AL23,"p")</f>
         <v>4</v>
       </c>
-      <c r="AN23" s="4" t="n">
+      <c r="AN23" s="2" t="n">
         <f aca="false">COUNTIF(W23:AL23,"M")</f>
         <v>1</v>
       </c>
-      <c r="AO23" s="4" t="n">
+      <c r="AO23" s="2" t="n">
         <f aca="false">COUNTIF(W23:AL23,"T")</f>
         <v>1</v>
       </c>
-      <c r="AP23" s="7" t="n">
+      <c r="AP23" s="6" t="n">
         <f aca="false">ROUND((AM23+AN23/2+AO23/4)*10/9,0)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
+    <row r="24" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q24" s="1" t="n">
+      <c r="B24" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7" t="n">
         <f aca="false">COUNTIF(E24:O24,"P")</f>
         <v>7</v>
       </c>
-      <c r="R24" s="1" t="n">
+      <c r="R24" s="7" t="n">
         <f aca="false">COUNTIF(E24:O24,"M")</f>
         <v>0</v>
       </c>
-      <c r="S24" s="1" t="n">
+      <c r="S24" s="7" t="n">
         <f aca="false">COUNTIF(E24:O24,"T")</f>
         <v>0</v>
       </c>
-      <c r="T24" s="1" t="n">
+      <c r="T24" s="7" t="n">
         <f aca="false">ROUND(Q24+R24/2+S24/4,0)</f>
         <v>7</v>
       </c>
-      <c r="V24" s="6" t="n">
+      <c r="U24" s="7"/>
+      <c r="V24" s="9" t="n">
         <f aca="false">ROUND(T24*10/$W$1,0)</f>
         <v>10</v>
       </c>
-      <c r="W24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC24" s="5" t="n">
+      <c r="W24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="X24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA24" s="7"/>
+      <c r="AB24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC24" s="10" t="n">
         <v>0.538194444444444</v>
       </c>
-      <c r="AD24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM24" s="4" t="n">
+      <c r="AD24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE24" s="7"/>
+      <c r="AF24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG24" s="7"/>
+      <c r="AH24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI24" s="7"/>
+      <c r="AJ24" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL24" s="7"/>
+      <c r="AM24" s="8" t="n">
         <f aca="false">COUNTIF(W24:AL24,"p")</f>
         <v>6</v>
       </c>
-      <c r="AN24" s="4" t="n">
+      <c r="AN24" s="8" t="n">
         <f aca="false">COUNTIF(W24:AL24,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO24" s="4" t="n">
+      <c r="AO24" s="8" t="n">
         <f aca="false">COUNTIF(W24:AL24,"T")</f>
         <v>1</v>
       </c>
-      <c r="AP24" s="7" t="n">
+      <c r="AP24" s="11" t="n">
         <f aca="false">ROUND((AM24+AN24/2+AO24/4)*10/9,0)</f>
         <v>7</v>
+      </c>
+      <c r="AQ24" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25" s="1" t="n">
         <f aca="false">COUNTIF(E3:E24,"P")</f>
@@ -3914,10 +4061,14 @@
         <f aca="false">COUNTIF(AK3:AK24,"P")</f>
         <v>13</v>
       </c>
+      <c r="AQ25" s="1" t="n">
+        <f aca="false">COUNTIF(AQ8:AQ24,"P")</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="X26" s="1" t="n">
         <f aca="false">COUNTIF(X3:X24,"M")</f>
@@ -3954,7 +4105,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X27" s="1" t="n">
         <f aca="false">COUNTIF(X3:X24,"T")</f>
@@ -3991,7 +4142,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AF28" s="1" t="n">
         <f aca="false">COUNTIF(AF3:AF24,"o")</f>
@@ -4012,7 +4163,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="X29" s="1" t="n">
         <f aca="false">SUM(X25:X27)</f>
@@ -4086,10 +4237,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>120</v>
@@ -4098,7 +4249,7 @@
         <v>121</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>122</v>
@@ -4112,7 +4263,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -4126,13 +4277,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>288</v>
@@ -4149,7 +4300,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -4163,13 +4314,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>289</v>
@@ -4186,7 +4337,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -4200,7 +4351,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -4214,13 +4365,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>290</v>
@@ -4237,13 +4388,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>291</v>
@@ -4265,10 +4416,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>250</v>
@@ -4282,13 +4433,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>292</v>
@@ -4310,10 +4461,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>293</v>
@@ -4327,7 +4478,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>1</v>
@@ -4341,13 +4492,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>294</v>
@@ -4364,13 +4515,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>295</v>
@@ -4387,7 +4538,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -4401,13 +4552,13 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>296</v>
@@ -4424,7 +4575,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>1</v>
@@ -4438,7 +4589,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>1</v>
@@ -4452,7 +4603,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>1</v>
@@ -4466,7 +4617,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>1</v>
@@ -4480,7 +4631,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>1</v>
@@ -4494,7 +4645,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>1</v>
@@ -4508,13 +4659,13 @@
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>297</v>
@@ -4536,10 +4687,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>298</v>
@@ -4550,10 +4701,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>299</v>
@@ -4567,7 +4718,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>1</v>
@@ -4616,10 +4767,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>120</v>
@@ -4633,13 +4784,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>300</v>
@@ -4653,13 +4804,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>301</v>
@@ -4673,13 +4824,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>302</v>
@@ -4693,13 +4844,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>303</v>
@@ -4713,7 +4864,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -4724,13 +4875,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>304</v>
@@ -4744,13 +4895,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>305</v>
@@ -4764,13 +4915,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>306</v>
@@ -4784,13 +4935,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>307</v>
@@ -4804,13 +4955,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>308</v>
@@ -4824,13 +4975,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>309</v>
@@ -4844,13 +4995,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>310</v>
@@ -4864,13 +5015,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>311</v>
@@ -4884,13 +5035,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>312</v>
@@ -4904,13 +5055,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>313</v>
@@ -4924,7 +5075,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -4935,13 +5086,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>314</v>
@@ -4955,13 +5106,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>315</v>
@@ -4975,13 +5126,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>316</v>
@@ -4995,13 +5146,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>317</v>
@@ -5015,13 +5166,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>318</v>
@@ -5035,13 +5186,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>319</v>
@@ -5066,7 +5217,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AP24"/>
+  <dimension ref="A1:AMM24"/>
   <sheetFormatPr defaultColWidth="9.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
@@ -5074,157 +5225,169 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="3" style="1" width="9.36"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="14" style="1" width="9.5"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="9.56"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="21" min="21" style="1" width="19.39"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="31" min="22" style="1" width="9.56"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="34" min="32" style="0" width="9.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1025" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="19.39"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="32" min="22" style="1" width="9.56"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="39" min="33" style="1" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="14.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1027" min="1027" style="1" width="9.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="2"/>
       <c r="T1" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="V1" s="3"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
       <c r="AI1" s="2"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
-      <c r="AL1" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
-      <c r="AN1" s="2"/>
+      <c r="AN1" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="AO1" s="2"/>
-      <c r="AP1" s="2"/>
+      <c r="AP1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="T2" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V2" s="3" t="n">
         <v>45877</v>
       </c>
       <c r="W2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE2" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK2" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="AG2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AH2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AN2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="AL2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="2"/>
       <c r="AP2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>10</v>
@@ -5235,7 +5398,7 @@
       <c r="G3" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I3" s="8" t="n">
+      <c r="I3" s="7" t="n">
         <v>7</v>
       </c>
       <c r="J3" s="3" t="n">
@@ -5252,14 +5415,14 @@
         <f aca="false">ROUND(AVERAGE(C3,E3,G3,L3),0)</f>
         <v>9</v>
       </c>
-      <c r="N3" s="1" t="str">
+      <c r="N3" s="6" t="str">
         <f aca="false">IF(M3&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O3" s="9" t="n">
+      <c r="O3" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="P3" s="10" t="n">
+      <c r="P3" s="13" t="n">
         <v>45783</v>
       </c>
       <c r="Q3" s="1" t="n">
@@ -5268,7 +5431,7 @@
       <c r="S3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T3" s="11" t="n">
+      <c r="T3" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S3,Q3,O3,M3),0)</f>
         <v>8</v>
       </c>
@@ -5278,40 +5441,40 @@
       <c r="AC3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AF3" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG3" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH3" s="0" t="n">
+      <c r="AG3" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI3" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ3" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AI3" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK3" s="4" t="n">
-        <f aca="false">AI3+AJ3/2</f>
+      <c r="AK3" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="2" t="n">
+        <f aca="false">AK3+AL3/2</f>
         <v>7.5</v>
       </c>
-      <c r="AL3" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF3,AG3,AH3,AK3),0)</f>
-        <v>7</v>
-      </c>
-      <c r="AM3" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T3,AL3),0)</f>
+      <c r="AN3" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG3,AI3,AJ3,AM3),0)</f>
+        <v>7</v>
+      </c>
+      <c r="AO3" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T3,AN3),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>10</v>
@@ -5336,7 +5499,7 @@
         <f aca="false">ROUND(AVERAGE(C4,E4,G4,L4),0)</f>
         <v>10</v>
       </c>
-      <c r="N4" s="1" t="str">
+      <c r="N4" s="6" t="str">
         <f aca="false">IF(M4&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -5349,7 +5512,7 @@
       <c r="S4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T4" s="11" t="n">
+      <c r="T4" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S4,Q4,O4,M4),0)</f>
         <v>9</v>
       </c>
@@ -5359,40 +5522,40 @@
       <c r="AC4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AF4" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG4" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH4" s="0" t="n">
+      <c r="AG4" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI4" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AI4" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ4" s="0" t="n">
+      <c r="AK4" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AK4" s="4" t="n">
-        <f aca="false">AI4+AJ4/2</f>
+      <c r="AM4" s="2" t="n">
+        <f aca="false">AK4+AL4/2</f>
         <v>11.5</v>
       </c>
-      <c r="AL4" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF4,AG4,AH4,AK4),0)</f>
-        <v>9</v>
-      </c>
-      <c r="AM4" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T4,AL4),0)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AN4" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG4,AI4,AJ4,AM4),0)</f>
+        <v>9</v>
+      </c>
+      <c r="AO4" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T4,AN4),0)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>9</v>
@@ -5403,7 +5566,7 @@
       <c r="G5" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="7" t="n">
         <v>9</v>
       </c>
       <c r="J5" s="3" t="n">
@@ -5420,14 +5583,14 @@
         <f aca="false">ROUND(AVERAGE(C5,E5,G5,L5),0)</f>
         <v>9</v>
       </c>
-      <c r="N5" s="1" t="str">
+      <c r="N5" s="6" t="str">
         <f aca="false">IF(M5&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O5" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="P5" s="10" t="n">
+      <c r="O5" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="P5" s="13" t="n">
         <v>45782</v>
       </c>
       <c r="Q5" s="1" t="n">
@@ -5436,47 +5599,47 @@
       <c r="S5" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T5" s="11" t="n">
+      <c r="T5" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S5,Q5,O5,M5),0)</f>
         <v>9</v>
       </c>
       <c r="AC5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AF5" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG5" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH5" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI5" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="4" t="n">
-        <f aca="false">AI5+AJ5/2</f>
-        <v>7</v>
-      </c>
-      <c r="AL5" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF5,AG5,AH5,AK5),0)</f>
+      <c r="AG5" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI5" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ5" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK5" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="2" t="n">
+        <f aca="false">AK5+AL5/2</f>
+        <v>7</v>
+      </c>
+      <c r="AN5" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG5,AI5,AJ5,AM5),0)</f>
         <v>8</v>
       </c>
-      <c r="AM5" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T5,AL5),0)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AO5" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T5,AN5),0)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>10</v>
@@ -5501,7 +5664,7 @@
         <f aca="false">ROUND(AVERAGE(C6,E6,G6,L6),0)</f>
         <v>10</v>
       </c>
-      <c r="N6" s="1" t="str">
+      <c r="N6" s="6" t="str">
         <f aca="false">IF(M6&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -5514,68 +5677,68 @@
       <c r="S6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="T6" s="11" t="n">
+      <c r="T6" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S6,Q6,O6,M6),0)</f>
         <v>8</v>
       </c>
       <c r="AC6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AF6" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG6" s="0" t="n">
+      <c r="AG6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AH6" s="0" t="n">
+      <c r="AJ6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AI6" s="0" t="n">
+      <c r="AK6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AJ6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK6" s="4" t="n">
-        <f aca="false">AI6+AJ6/2</f>
+      <c r="AL6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="2" t="n">
+        <f aca="false">AK6+AL6/2</f>
         <v>8.5</v>
       </c>
-      <c r="AL6" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF6,AG6,AH6,AK6),0)</f>
-        <v>9</v>
-      </c>
-      <c r="AM6" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T6,AL6),0)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AN6" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG6,AI6,AJ6,AM6),0)</f>
+        <v>9</v>
+      </c>
+      <c r="AO6" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T6,AN6),0)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="C7" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>45764</v>
       </c>
-      <c r="E7" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="9" t="n">
+      <c r="E7" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H7" s="13" t="n">
         <v>45875</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="J7" s="10" t="n">
+      <c r="J7" s="13" t="n">
         <v>45875</v>
       </c>
       <c r="K7" s="1" t="n">
@@ -5589,14 +5752,14 @@
         <f aca="false">ROUND(AVERAGE(C7,E7,G7,L7),0)</f>
         <v>7</v>
       </c>
-      <c r="N7" s="1" t="str">
+      <c r="N7" s="6" t="str">
         <f aca="false">IF(M7&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O7" s="9" t="n">
+      <c r="O7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="P7" s="10" t="n">
+      <c r="P7" s="13" t="n">
         <v>45875</v>
       </c>
       <c r="Q7" s="1" t="n">
@@ -5608,141 +5771,176 @@
       <c r="S7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="T7" s="11" t="n">
+      <c r="T7" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S7,Q7,O7,M7),0)</f>
         <v>7</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AC7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AF7" s="1" t="n">
+      <c r="AG7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AG7" s="0" t="n">
+      <c r="AI7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AH7" s="0" t="n">
+      <c r="AJ7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AI7" s="0" t="n">
+      <c r="AK7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AJ7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK7" s="4" t="n">
-        <f aca="false">AI7+AJ7/2</f>
+      <c r="AL7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="2" t="n">
+        <f aca="false">AK7+AL7/2</f>
         <v>4.5</v>
       </c>
-      <c r="AL7" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF7,AG7,AH7,AK7),0)</f>
-        <v>7</v>
-      </c>
-      <c r="AM7" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T7,AL7),0)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="AN7" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG7,AI7,AJ7,AM7),0)</f>
+        <v>7</v>
+      </c>
+      <c r="AO7" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T7,AN7),0)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" s="8" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="D8" s="10" t="n">
+      <c r="B8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" s="14" t="n">
         <v>45842</v>
       </c>
-      <c r="E8" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="8" t="n">
+      <c r="E8" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" s="14" t="n">
         <v>45784</v>
       </c>
-      <c r="K8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1" t="n">
+      <c r="K8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7" t="n">
         <f aca="false">I8+K8/2</f>
         <v>5</v>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="M8" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(C8,E8,G8,L8),0)</f>
         <v>8</v>
       </c>
-      <c r="N8" s="1" t="str">
+      <c r="N8" s="11" t="str">
         <f aca="false">IF(M8&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O8" s="9" t="n">
+      <c r="O8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="P8" s="10" t="n">
+      <c r="P8" s="14" t="n">
         <v>45784</v>
       </c>
-      <c r="Q8" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="S8" s="1" t="n">
+      <c r="Q8" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7" t="n">
         <v>10</v>
       </c>
       <c r="T8" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(S8,Q8,O8,M8),0)</f>
         <v>9</v>
       </c>
-      <c r="AC8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG8" s="0" t="n">
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AH8" s="0" t="n">
+      <c r="X8" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AI8" s="0" t="n">
+      <c r="Y8" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD8" s="16" t="n">
+        <v>45996</v>
+      </c>
+      <c r="AE8" s="7"/>
+      <c r="AF8" s="7"/>
+      <c r="AG8" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH8" s="16" t="n">
+        <v>45996</v>
+      </c>
+      <c r="AI8" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ8" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AJ8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK8" s="4" t="n">
-        <f aca="false">AI8+AJ8/2</f>
+      <c r="AL8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="8" t="n">
+        <f aca="false">AK8+AL8/2</f>
         <v>5.5</v>
       </c>
-      <c r="AL8" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF8,AG8,AH8,AK8),0)</f>
+      <c r="AN8" s="11" t="n">
+        <f aca="false">ROUND(AVERAGE(AG8,AI8,AJ8,AM8),0)</f>
+        <v>7</v>
+      </c>
+      <c r="AO8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AM8" s="7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AP8" s="8" t="n">
+        <f aca="false">ROUND(AVERAGE(AC8,AG8,AI8,AJ8),0)</f>
+        <v>9</v>
+      </c>
+      <c r="AQ8" s="11" t="n">
+        <f aca="false">ROUND(AP8*6/10,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AR8" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AMM8" s="7"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>10</v>
@@ -5767,7 +5965,7 @@
         <f aca="false">ROUND(AVERAGE(C9,E9,G9,L9),0)</f>
         <v>10</v>
       </c>
-      <c r="N9" s="1" t="str">
+      <c r="N9" s="6" t="str">
         <f aca="false">IF(M9&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -5780,47 +5978,47 @@
       <c r="S9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T9" s="11" t="n">
+      <c r="T9" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S9,Q9,O9,M9),0)</f>
         <v>9</v>
       </c>
       <c r="AC9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AF9" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG9" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH9" s="0" t="n">
+      <c r="AG9" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI9" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AI9" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK9" s="4" t="n">
-        <f aca="false">AI9+AJ9/2</f>
+      <c r="AK9" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="2" t="n">
+        <f aca="false">AK9+AL9/2</f>
         <v>9.5</v>
       </c>
-      <c r="AL9" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF9,AG9,AH9,AK9),0)</f>
-        <v>9</v>
-      </c>
-      <c r="AM9" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T9,AL9),0)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AN9" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG9,AI9,AJ9,AM9),0)</f>
+        <v>9</v>
+      </c>
+      <c r="AO9" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T9,AN9),0)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>9</v>
@@ -5845,7 +6043,7 @@
         <f aca="false">ROUND(AVERAGE(C10,E10,G10,L10),0)</f>
         <v>10</v>
       </c>
-      <c r="N10" s="1" t="str">
+      <c r="N10" s="6" t="str">
         <f aca="false">IF(M10&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -5858,47 +6056,47 @@
       <c r="S10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T10" s="11" t="n">
+      <c r="T10" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S10,Q10,O10,M10),0)</f>
         <v>10</v>
       </c>
       <c r="AC10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AF10" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG10" s="0" t="n">
+      <c r="AG10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AH10" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI10" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ10" s="0" t="n">
+      <c r="AJ10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AK10" s="4" t="n">
-        <f aca="false">AI10+AJ10/2</f>
-        <v>10</v>
-      </c>
-      <c r="AL10" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF10,AG10,AH10,AK10),0)</f>
-        <v>10</v>
-      </c>
-      <c r="AM10" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T10,AL10),0)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM10" s="2" t="n">
+        <f aca="false">AK10+AL10/2</f>
+        <v>10</v>
+      </c>
+      <c r="AN10" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG10,AI10,AJ10,AM10),0)</f>
+        <v>10</v>
+      </c>
+      <c r="AO10" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T10,AN10),0)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>10</v>
@@ -5923,7 +6121,7 @@
         <f aca="false">ROUND(AVERAGE(C11,E11,G11,L11),0)</f>
         <v>10</v>
       </c>
-      <c r="N11" s="1" t="str">
+      <c r="N11" s="6" t="str">
         <f aca="false">IF(M11&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -5936,128 +6134,154 @@
       <c r="S11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T11" s="11" t="n">
+      <c r="T11" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S11,Q11,O11,M11),0)</f>
         <v>9</v>
       </c>
       <c r="AC11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AF11" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG11" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH11" s="0" t="n">
+      <c r="AG11" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI11" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AI11" s="0" t="n">
+      <c r="AK11" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AJ11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="4" t="n">
-        <f aca="false">AI11+AJ11/2</f>
+      <c r="AL11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="2" t="n">
+        <f aca="false">AK11+AL11/2</f>
         <v>4</v>
       </c>
-      <c r="AL11" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF11,AG11,AH11,AK11),0)</f>
-        <v>7</v>
-      </c>
-      <c r="AM11" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T11,AL11),0)</f>
+      <c r="AN11" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG11,AI11,AJ11,AM11),0)</f>
+        <v>7</v>
+      </c>
+      <c r="AO11" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T11,AN11),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1" t="n">
+    <row r="12" s="8" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L12" s="1" t="n">
+      <c r="L12" s="7" t="n">
         <f aca="false">I12+K12/2</f>
         <v>2.5</v>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="M12" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(C12,E12,G12,L12),0)</f>
         <v>1</v>
       </c>
-      <c r="N12" s="1" t="str">
+      <c r="N12" s="11" t="str">
         <f aca="false">IF(M12&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="O12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="1" t="n">
+      <c r="O12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7" t="n">
         <v>8.25</v>
       </c>
-      <c r="S12" s="1" t="n">
+      <c r="R12" s="7"/>
+      <c r="S12" s="7" t="n">
         <v>10</v>
       </c>
       <c r="T12" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(S12,Q12,O12,M12),0)</f>
         <v>5</v>
       </c>
-      <c r="V12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" s="1" t="n">
+      <c r="U12" s="7"/>
+      <c r="V12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="7"/>
+      <c r="AC12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="7"/>
+      <c r="AE12" s="7"/>
+      <c r="AF12" s="7"/>
+      <c r="AG12" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AG12" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH12" s="0" t="n">
+      <c r="AH12" s="7"/>
+      <c r="AI12" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AI12" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="4" t="n">
-        <f aca="false">AI12+AJ12/2</f>
+      <c r="AK12" s="7" t="n">
         <v>7</v>
       </c>
       <c r="AL12" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF12,AG12,AH12,AK12),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM12" s="8" t="n">
+        <f aca="false">AK12+AL12/2</f>
+        <v>7</v>
+      </c>
+      <c r="AN12" s="11" t="n">
+        <f aca="false">ROUND(AVERAGE(AG12,AI12,AJ12,AM12),0)</f>
         <v>6</v>
       </c>
-      <c r="AM12" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T12,AL12),0)</f>
+      <c r="AO12" s="7" t="n">
+        <f aca="false">ROUND(AVERAGE(T12,AN12),0)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AP12" s="8" t="n">
+        <f aca="false">ROUND(AVERAGE(AC12,AG12,AI12,AJ12),0)</f>
+        <v>5</v>
+      </c>
+      <c r="AQ12" s="11" t="n">
+        <f aca="false">ROUND(AP12*6/10,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AMM12" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>10</v>
@@ -6082,7 +6306,7 @@
         <f aca="false">ROUND(AVERAGE(C13,E13,G13,L13),0)</f>
         <v>10</v>
       </c>
-      <c r="N13" s="1" t="str">
+      <c r="N13" s="6" t="str">
         <f aca="false">IF(M13&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -6095,47 +6319,47 @@
       <c r="S13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T13" s="11" t="n">
+      <c r="T13" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S13,Q13,O13,M13),0)</f>
         <v>10</v>
       </c>
       <c r="AC13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AF13" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG13" s="0" t="n">
+      <c r="AG13" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI13" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AH13" s="0" t="n">
+      <c r="AJ13" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AI13" s="0" t="n">
+      <c r="AK13" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AJ13" s="0" t="n">
+      <c r="AL13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AK13" s="4" t="n">
-        <f aca="false">AI13+AJ13/2</f>
-        <v>9</v>
-      </c>
-      <c r="AL13" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF13,AG13,AH13,AK13),0)</f>
-        <v>9</v>
-      </c>
-      <c r="AM13" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T13,AL13),0)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AM13" s="2" t="n">
+        <f aca="false">AK13+AL13/2</f>
+        <v>9</v>
+      </c>
+      <c r="AN13" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG13,AI13,AJ13,AM13),0)</f>
+        <v>9</v>
+      </c>
+      <c r="AO13" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T13,AN13),0)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>7</v>
@@ -6160,7 +6384,7 @@
         <f aca="false">ROUND(AVERAGE(C14,E14,G14,L14),0)</f>
         <v>8</v>
       </c>
-      <c r="N14" s="1" t="str">
+      <c r="N14" s="6" t="str">
         <f aca="false">IF(M14&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -6173,140 +6397,162 @@
       <c r="S14" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="T14" s="11" t="n">
+      <c r="T14" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S14,Q14,O14,M14),0)</f>
         <v>9</v>
       </c>
       <c r="AC14" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AF14" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG14" s="0" t="n">
+      <c r="AG14" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AH14" s="0" t="n">
+      <c r="AJ14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AI14" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="4" t="n">
-        <f aca="false">AI14+AJ14/2</f>
-        <v>7</v>
-      </c>
-      <c r="AL14" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF14,AG14,AH14,AK14),0)</f>
+      <c r="AK14" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="2" t="n">
+        <f aca="false">AK14+AL14/2</f>
+        <v>7</v>
+      </c>
+      <c r="AN14" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG14,AI14,AJ14,AM14),0)</f>
         <v>8</v>
       </c>
-      <c r="AM14" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T14,AL14),0)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
+      <c r="AO14" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T14,AN14),0)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" s="8" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" s="9" t="n">
+      <c r="B15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F15" s="14" t="n">
         <v>45877</v>
       </c>
-      <c r="G15" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" s="9" t="n">
+      <c r="G15" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="J15" s="10" t="n">
+      <c r="J15" s="14" t="n">
         <v>45877</v>
       </c>
-      <c r="K15" s="1" t="n">
+      <c r="K15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="1" t="n">
+      <c r="L15" s="7" t="n">
         <f aca="false">I15+K15/2</f>
         <v>5.5</v>
       </c>
-      <c r="M15" s="1" t="n">
+      <c r="M15" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(C15,E15,G15,L15),0)</f>
         <v>7</v>
       </c>
-      <c r="N15" s="1" t="str">
+      <c r="N15" s="11" t="str">
         <f aca="false">IF(M15&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O15" s="9" t="n">
+      <c r="O15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="P15" s="10" t="n">
+      <c r="P15" s="14" t="n">
         <v>45877</v>
       </c>
-      <c r="Q15" s="1" t="n">
+      <c r="Q15" s="7" t="n">
         <v>7.25</v>
       </c>
-      <c r="S15" s="1" t="n">
+      <c r="R15" s="7"/>
+      <c r="S15" s="7" t="n">
         <v>9</v>
       </c>
       <c r="T15" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(S15,Q15,O15,M15),0)</f>
         <v>7</v>
       </c>
-      <c r="U15" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" s="1" t="n">
+      <c r="U15" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="V15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7"/>
+      <c r="AC15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="7"/>
+      <c r="AE15" s="7"/>
+      <c r="AF15" s="7"/>
+      <c r="AG15" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AG15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI15" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ15" s="0" t="n">
+      <c r="AH15" s="7"/>
+      <c r="AI15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK15" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AK15" s="4" t="n">
-        <f aca="false">AI15+AJ15/2</f>
-        <v>10</v>
-      </c>
-      <c r="AL15" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF15,AG15,AH15,AK15),0)</f>
+      <c r="AM15" s="8" t="n">
+        <f aca="false">AK15+AL15/2</f>
+        <v>10</v>
+      </c>
+      <c r="AN15" s="11" t="n">
+        <f aca="false">ROUND(AVERAGE(AG15,AI15,AJ15,AM15),0)</f>
         <v>5</v>
       </c>
-      <c r="AM15" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T15,AL15),0)</f>
+      <c r="AO15" s="7" t="n">
+        <f aca="false">ROUND(AVERAGE(T15,AN15),0)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AP15" s="8" t="n">
+        <f aca="false">ROUND(AVERAGE(AC15,AG15,AI15,AJ15),0)</f>
+        <v>3</v>
+      </c>
+      <c r="AQ15" s="11" t="n">
+        <f aca="false">ROUND(AP15*6/10,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AMM15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>9</v>
@@ -6331,7 +6577,7 @@
         <f aca="false">ROUND(AVERAGE(C16,E16,G16,L16),0)</f>
         <v>9</v>
       </c>
-      <c r="N16" s="1" t="str">
+      <c r="N16" s="6" t="str">
         <f aca="false">IF(M16&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -6344,47 +6590,47 @@
       <c r="S16" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="T16" s="11" t="n">
+      <c r="T16" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S16,Q16,O16,M16),0)</f>
         <v>8</v>
       </c>
       <c r="AC16" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AF16" s="1" t="n">
+      <c r="AG16" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AG16" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH16" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI16" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ16" s="0" t="n">
+      <c r="AI16" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ16" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK16" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL16" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AK16" s="4" t="n">
-        <f aca="false">AI16+AJ16/2</f>
+      <c r="AM16" s="2" t="n">
+        <f aca="false">AK16+AL16/2</f>
         <v>11</v>
       </c>
-      <c r="AL16" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF16,AG16,AH16,AK16),0)</f>
-        <v>10</v>
-      </c>
-      <c r="AM16" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T16,AL16),0)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AN16" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG16,AI16,AJ16,AM16),0)</f>
+        <v>10</v>
+      </c>
+      <c r="AO16" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T16,AN16),0)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>10</v>
@@ -6395,7 +6641,7 @@
       <c r="G17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="I17" s="7" t="n">
         <v>7</v>
       </c>
       <c r="J17" s="3" t="n">
@@ -6412,14 +6658,14 @@
         <f aca="false">ROUND(AVERAGE(C17,E17,G17,L17),0)</f>
         <v>9</v>
       </c>
-      <c r="N17" s="1" t="str">
+      <c r="N17" s="6" t="str">
         <f aca="false">IF(M17&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O17" s="9" t="n">
+      <c r="O17" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="P17" s="10" t="n">
+      <c r="P17" s="13" t="n">
         <v>45782</v>
       </c>
       <c r="Q17" s="1" t="n">
@@ -6428,212 +6674,263 @@
       <c r="S17" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T17" s="11" t="n">
+      <c r="T17" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S17,Q17,O17,M17),0)</f>
         <v>8</v>
       </c>
       <c r="AC17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AF17" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG17" s="0" t="n">
+      <c r="AG17" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI17" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AH17" s="0" t="n">
+      <c r="AJ17" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AI17" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK17" s="4" t="n">
-        <f aca="false">AI17+AJ17/2</f>
+      <c r="AK17" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM17" s="2" t="n">
+        <f aca="false">AK17+AL17/2</f>
         <v>7.5</v>
       </c>
-      <c r="AL17" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF17,AG17,AH17,AK17),0)</f>
+      <c r="AN17" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG17,AI17,AJ17,AM17),0)</f>
         <v>8</v>
       </c>
-      <c r="AM17" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T17,AL17),0)</f>
+      <c r="AO17" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T17,AN17),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
+    <row r="18" s="8" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D18" s="10" t="n">
+      <c r="B18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" s="14" t="n">
         <v>45877</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="1" t="n">
+      <c r="E18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="7" t="n">
         <f aca="false">I18+K18/2</f>
         <v>1</v>
       </c>
-      <c r="M18" s="1" t="n">
+      <c r="M18" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(C18,E18,G18,L18),0)</f>
         <v>3</v>
       </c>
-      <c r="N18" s="1" t="str">
+      <c r="N18" s="11" t="str">
         <f aca="false">IF(M18&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="O18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" s="1" t="n">
+      <c r="O18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7" t="n">
         <v>7</v>
       </c>
       <c r="T18" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(S18,Q18,O18,M18),0)</f>
         <v>3</v>
       </c>
-      <c r="V18" s="1" t="s">
+      <c r="U18" s="7"/>
+      <c r="V18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="7"/>
+      <c r="AB18" s="7"/>
+      <c r="AC18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="7"/>
+      <c r="AE18" s="7"/>
+      <c r="AF18" s="7"/>
+      <c r="AG18" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH18" s="7"/>
+      <c r="AI18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="8" t="n">
+        <f aca="false">AK18+AL18/2</f>
+        <v>2</v>
+      </c>
+      <c r="AN18" s="11" t="n">
+        <f aca="false">ROUND(AVERAGE(AG18,AI18,AJ18,AM18),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AO18" s="7" t="n">
+        <f aca="false">ROUND(AVERAGE(T18,AN18),0)</f>
+        <v>3</v>
+      </c>
+      <c r="AP18" s="8" t="n">
+        <f aca="false">ROUND(AVERAGE(AC18,AG18,AI18,AJ18),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AQ18" s="11" t="n">
+        <f aca="false">ROUND(AP18*6/10,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AMM18" s="7"/>
+    </row>
+    <row r="19" s="8" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="AC18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF18" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI18" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="4" t="n">
-        <f aca="false">AI18+AJ18/2</f>
-        <v>2</v>
-      </c>
-      <c r="AL18" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF18,AG18,AH18,AK18),0)</f>
-        <v>2</v>
-      </c>
-      <c r="AM18" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T18,AL18),0)</f>
+      <c r="B19" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>45784</v>
+      </c>
+      <c r="K19" s="7" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>45784</v>
-      </c>
-      <c r="K19" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" s="1" t="n">
+      <c r="L19" s="7" t="n">
         <f aca="false">I19+K19/2</f>
         <v>7.5</v>
       </c>
-      <c r="M19" s="1" t="n">
+      <c r="M19" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(C19,E19,G19,L19),0)</f>
         <v>9</v>
       </c>
-      <c r="N19" s="1" t="str">
+      <c r="N19" s="11" t="str">
         <f aca="false">IF(M19&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S19" s="1" t="n">
+      <c r="O19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7" t="n">
         <v>9</v>
       </c>
       <c r="T19" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(S19,Q19,O19,M19),0)</f>
         <v>7</v>
       </c>
-      <c r="AC19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" s="1" t="n">
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="7"/>
+      <c r="AA19" s="7"/>
+      <c r="AB19" s="7"/>
+      <c r="AC19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="7"/>
+      <c r="AE19" s="7"/>
+      <c r="AF19" s="7"/>
+      <c r="AG19" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AG19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI19" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK19" s="4" t="n">
-        <f aca="false">AI19+AJ19/2</f>
+      <c r="AH19" s="7"/>
+      <c r="AI19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM19" s="8" t="n">
+        <f aca="false">AK19+AL19/2</f>
         <v>7.5</v>
       </c>
-      <c r="AL19" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF19,AG19,AH19,AK19),0)</f>
+      <c r="AN19" s="11" t="n">
+        <f aca="false">ROUND(AVERAGE(AG19,AI19,AJ19,AM19),0)</f>
         <v>4</v>
       </c>
-      <c r="AM19" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T19,AL19),0)</f>
+      <c r="AO19" s="7" t="n">
+        <f aca="false">ROUND(AVERAGE(T19,AN19),0)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AP19" s="8" t="n">
+        <f aca="false">ROUND(AVERAGE(AC19,AG19,AI19,AJ19),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AQ19" s="11" t="n">
+        <f aca="false">ROUND(AP19*6/10,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AMM19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>9</v>
@@ -6658,7 +6955,7 @@
         <f aca="false">ROUND(AVERAGE(C20,E20,G20,L20),0)</f>
         <v>7</v>
       </c>
-      <c r="N20" s="1" t="str">
+      <c r="N20" s="6" t="str">
         <f aca="false">IF(M20&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -6671,50 +6968,50 @@
       <c r="S20" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T20" s="11" t="n">
+      <c r="T20" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S20,Q20,O20,M20),0)</f>
         <v>6</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AC20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AF20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI20" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK20" s="4" t="n">
-        <f aca="false">AI20+AJ20/2</f>
+      <c r="AG20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM20" s="2" t="n">
+        <f aca="false">AK20+AL20/2</f>
         <v>7.5</v>
       </c>
-      <c r="AL20" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF20,AG20,AH20,AK20),0)</f>
+      <c r="AN20" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG20,AI20,AJ20,AM20),0)</f>
         <v>3</v>
       </c>
-      <c r="AM20" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T20,AL20),0)</f>
+      <c r="AO20" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T20,AN20),0)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>9</v>
@@ -6739,7 +7036,7 @@
         <f aca="false">ROUND(AVERAGE(C21,E21,G21,L21),0)</f>
         <v>8</v>
       </c>
-      <c r="N21" s="1" t="str">
+      <c r="N21" s="6" t="str">
         <f aca="false">IF(M21&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -6752,47 +7049,48 @@
       <c r="S21" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="T21" s="11" t="n">
+      <c r="T21" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S21,Q21,O21,M21),0)</f>
         <v>7</v>
       </c>
       <c r="AC21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AF21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG21" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH21" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="4" t="n">
-        <f aca="false">AI21+AJ21/2</f>
-        <v>0</v>
-      </c>
-      <c r="AL21" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF21,AG21,AH21,AK21),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AM21" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T21,AL21),0)</f>
+      <c r="AG21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH21" s="2"/>
+      <c r="AI21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="2" t="n">
+        <f aca="false">AK21+AL21/2</f>
+        <v>0</v>
+      </c>
+      <c r="AN21" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG21,AI21,AJ21,AM21),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO21" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T21,AN21),0)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>10</v>
@@ -6803,7 +7101,7 @@
       <c r="G22" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="I22" s="17" t="n">
         <v>5</v>
       </c>
       <c r="J22" s="3" t="n">
@@ -6820,14 +7118,14 @@
         <f aca="false">ROUND(AVERAGE(C22,E22,G22,L22),0)</f>
         <v>8</v>
       </c>
-      <c r="N22" s="1" t="str">
+      <c r="N22" s="6" t="str">
         <f aca="false">IF(M22&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O22" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="P22" s="10" t="n">
+      <c r="O22" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="P22" s="13" t="n">
         <v>45784</v>
       </c>
       <c r="Q22" s="1" t="n">
@@ -6836,47 +7134,47 @@
       <c r="S22" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T22" s="11" t="n">
+      <c r="T22" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S22,Q22,O22,M22),0)</f>
         <v>9</v>
       </c>
       <c r="AC22" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AF22" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG22" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH22" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI22" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK22" s="4" t="n">
-        <f aca="false">AI22+AJ22/2</f>
+      <c r="AG22" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI22" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ22" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK22" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM22" s="2" t="n">
+        <f aca="false">AK22+AL22/2</f>
         <v>7.5</v>
       </c>
-      <c r="AL22" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF22,AG22,AH22,AK22),0)</f>
-        <v>7</v>
-      </c>
-      <c r="AM22" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T22,AL22),0)</f>
+      <c r="AN22" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG22,AI22,AJ22,AM22),0)</f>
+        <v>7</v>
+      </c>
+      <c r="AO22" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T22,AN22),0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>9</v>
@@ -6901,14 +7199,14 @@
         <f aca="false">ROUND(AVERAGE(C23,E23,G23,L23),0)</f>
         <v>10</v>
       </c>
-      <c r="N23" s="1" t="str">
+      <c r="N23" s="6" t="str">
         <f aca="false">IF(M23&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O23" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="P23" s="10" t="n">
+      <c r="O23" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="P23" s="13" t="n">
         <v>45782</v>
       </c>
       <c r="Q23" s="1" t="n">
@@ -6917,118 +7215,145 @@
       <c r="S23" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T23" s="11" t="n">
+      <c r="T23" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(S23,Q23,O23,M23),0)</f>
         <v>8</v>
       </c>
       <c r="AC23" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AF23" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG23" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH23" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI23" s="0" t="n">
+      <c r="AG23" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI23" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ23" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK23" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AJ23" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK23" s="4" t="n">
-        <f aca="false">AI23+AJ23/2</f>
+      <c r="AL23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM23" s="2" t="n">
+        <f aca="false">AK23+AL23/2</f>
         <v>5.5</v>
       </c>
-      <c r="AL23" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF23,AG23,AH23,AK23),0)</f>
-        <v>9</v>
-      </c>
-      <c r="AM23" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T23,AL23),0)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
+      <c r="AN23" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AG23,AI23,AJ23,AM23),0)</f>
+        <v>9</v>
+      </c>
+      <c r="AO23" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(T23,AN23),0)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" s="8" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="G24" s="1" t="n">
+      <c r="B24" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I24" s="1" t="n">
+      <c r="H24" s="7"/>
+      <c r="I24" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="K24" s="1" t="n">
+      <c r="J24" s="7"/>
+      <c r="K24" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L24" s="1" t="n">
+      <c r="L24" s="7" t="n">
         <f aca="false">I24+K24/2</f>
         <v>7.5</v>
       </c>
-      <c r="M24" s="1" t="n">
+      <c r="M24" s="7" t="n">
         <f aca="false">ROUND(AVERAGE(C24,E24,G24,L24),0)</f>
         <v>9</v>
       </c>
-      <c r="N24" s="1" t="str">
+      <c r="N24" s="11" t="str">
         <f aca="false">IF(M24&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S24" s="1" t="n">
+      <c r="O24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7" t="n">
         <v>10</v>
       </c>
       <c r="T24" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(S24,Q24,O24,M24),0)</f>
         <v>7</v>
       </c>
-      <c r="AC24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" s="1" t="n">
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7"/>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="7"/>
+      <c r="AA24" s="7"/>
+      <c r="AB24" s="7"/>
+      <c r="AC24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="7"/>
+      <c r="AE24" s="7"/>
+      <c r="AF24" s="7"/>
+      <c r="AG24" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AG24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI24" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="4" t="n">
-        <f aca="false">AI24+AJ24/2</f>
+      <c r="AH24" s="7"/>
+      <c r="AI24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK24" s="7" t="n">
         <v>7</v>
       </c>
       <c r="AL24" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(AF24,AG24,AH24,AK24),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM24" s="8" t="n">
+        <f aca="false">AK24+AL24/2</f>
+        <v>7</v>
+      </c>
+      <c r="AN24" s="11" t="n">
+        <f aca="false">ROUND(AVERAGE(AG24,AI24,AJ24,AM24),0)</f>
         <v>3</v>
       </c>
-      <c r="AM24" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(T24,AL24),0)</f>
+      <c r="AO24" s="7" t="n">
+        <f aca="false">ROUND(AVERAGE(T24,AN24),0)</f>
         <v>5</v>
       </c>
+      <c r="AP24" s="8" t="n">
+        <f aca="false">ROUND(AVERAGE(AC24,AG24,AI24,AJ24),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AQ24" s="11" t="n">
+        <f aca="false">ROUND(AP24*6/10,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AMM24" s="7"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="N3:N24">
@@ -7048,7 +7373,7 @@
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL3:AL24">
+  <conditionalFormatting sqref="AN3:AN24">
     <cfRule type="cellIs" priority="6" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
@@ -7060,7 +7385,7 @@
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM3:AM24">
+  <conditionalFormatting sqref="AO3:AO24">
     <cfRule type="cellIs" priority="9" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
@@ -7072,9 +7397,17 @@
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI3:AI25">
+  <conditionalFormatting sqref="AK3:AK25">
     <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AQ8:AQ24">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>4</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7097,31 +7430,31 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="3" min="3" style="0" width="9.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16361" style="0" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="3" min="3" style="1" width="9.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16361" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="n">
         <v>45737</v>
       </c>
-      <c r="D1" s="13" t="n">
+      <c r="D1" s="3" t="n">
         <v>45919</v>
       </c>
-      <c r="E1" s="13" t="n">
+      <c r="E1" s="3" t="n">
         <v>45954</v>
       </c>
-      <c r="F1" s="13" t="n">
+      <c r="F1" s="3" t="n">
         <v>45961</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>115</v>
+      <c r="G1" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7129,15 +7462,15 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="4" t="n">
+      <c r="F2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <f aca="false">SUM(D2:F2)</f>
         <v>1</v>
       </c>
@@ -7147,18 +7480,18 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="0" t="n">
+      <c r="D3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="2" t="n">
         <f aca="false">SUM(D3:F3)</f>
         <v>3</v>
       </c>
@@ -7168,12 +7501,12 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="2" t="n">
         <f aca="false">SUM(D4:F4)</f>
         <v>0</v>
       </c>
@@ -7183,15 +7516,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="n">
+      <c r="F5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <f aca="false">SUM(D5:F5)</f>
         <v>1</v>
       </c>
@@ -7201,15 +7534,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="n">
+      <c r="D6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <f aca="false">SUM(D6:F6)</f>
         <v>1</v>
       </c>
@@ -7219,15 +7552,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="n">
+      <c r="D7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <f aca="false">SUM(D7:F7)</f>
         <v>1</v>
       </c>
@@ -7237,15 +7570,15 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4" t="n">
+      <c r="D8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <f aca="false">SUM(D8:F8)</f>
         <v>1</v>
       </c>
@@ -7255,18 +7588,18 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="n">
+      <c r="D9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <f aca="false">SUM(D9:F9)</f>
         <v>2</v>
       </c>
@@ -7276,12 +7609,12 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="2" t="n">
         <f aca="false">SUM(D10:F10)</f>
         <v>0</v>
       </c>
@@ -7291,12 +7624,12 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="2" t="n">
         <f aca="false">SUM(D11:F11)</f>
         <v>0</v>
       </c>
@@ -7306,18 +7639,18 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="n">
+      <c r="D12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <f aca="false">SUM(D12:F12)</f>
         <v>2</v>
       </c>
@@ -7327,12 +7660,12 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="2" t="n">
         <f aca="false">SUM(D13:F13)</f>
         <v>0</v>
       </c>
@@ -7342,18 +7675,18 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="n">
+      <c r="D14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <f aca="false">SUM(D14:F14)</f>
         <v>2</v>
       </c>
@@ -7363,18 +7696,18 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="n">
+      <c r="D15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <f aca="false">SUM(D15:F15)</f>
         <v>2</v>
       </c>
@@ -7384,15 +7717,15 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="4" t="n">
+      <c r="D16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <f aca="false">SUM(D16:F16)</f>
         <v>1</v>
       </c>
@@ -7402,12 +7735,12 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="2" t="n">
         <f aca="false">SUM(D17:F17)</f>
         <v>0</v>
       </c>
@@ -7417,15 +7750,15 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4" t="n">
+      <c r="F18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="n">
         <f aca="false">SUM(D18:F18)</f>
         <v>1</v>
       </c>
@@ -7435,15 +7768,15 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="4" t="n">
+      <c r="F19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="n">
         <f aca="false">SUM(D19:F19)</f>
         <v>1</v>
       </c>
@@ -7453,12 +7786,12 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="2" t="n">
         <f aca="false">SUM(D20:F20)</f>
         <v>0</v>
       </c>
@@ -7468,15 +7801,15 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="4" t="n">
+      <c r="F21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="n">
         <f aca="false">SUM(D21:F21)</f>
         <v>1</v>
       </c>
@@ -7486,15 +7819,15 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="4" t="n">
+      <c r="F22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="n">
         <f aca="false">SUM(D22:F22)</f>
         <v>1</v>
       </c>
@@ -7504,12 +7837,12 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="2" t="n">
         <f aca="false">SUM(D23:F23)</f>
         <v>0</v>
       </c>
@@ -7540,7 +7873,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>119</v>
@@ -7552,7 +7885,7 @@
         <v>121</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>122</v>
@@ -7566,10 +7899,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>124</v>
@@ -7589,10 +7922,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>126</v>
@@ -7612,10 +7945,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>128</v>
@@ -7635,10 +7968,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>130</v>
@@ -7658,7 +7991,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -7672,7 +8005,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -7686,10 +8019,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>132</v>
@@ -7709,10 +8042,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>134</v>
@@ -7737,7 +8070,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>136</v>
@@ -7754,10 +8087,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>128</v>
@@ -7777,7 +8110,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>1</v>
@@ -7791,10 +8124,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>139</v>
@@ -7814,10 +8147,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>141</v>
@@ -7837,10 +8170,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>143</v>
@@ -7860,10 +8193,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>145</v>
@@ -7883,10 +8216,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>147</v>
@@ -7906,7 +8239,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>1</v>
@@ -7920,10 +8253,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>149</v>
@@ -7943,10 +8276,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>151</v>
@@ -7966,10 +8299,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>153</v>
@@ -7989,10 +8322,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>155</v>
@@ -8012,10 +8345,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>157</v>
@@ -8040,7 +8373,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>159</v>
@@ -8054,7 +8387,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>136</v>
@@ -8071,10 +8404,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>162</v>
@@ -8116,7 +8449,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>119</v>
@@ -8130,7 +8463,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>165</v>
@@ -8168,7 +8501,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>119</v>
@@ -8180,7 +8513,7 @@
         <v>121</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>122</v>
@@ -8194,10 +8527,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>167</v>
@@ -8217,10 +8550,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>169</v>
@@ -8240,10 +8573,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>171</v>
@@ -8263,10 +8596,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>172</v>
@@ -8286,7 +8619,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -8300,7 +8633,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -8314,10 +8647,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>174</v>
@@ -8337,10 +8670,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>176</v>
@@ -8360,10 +8693,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>178</v>
@@ -8383,7 +8716,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -8397,10 +8730,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>179</v>
@@ -8420,10 +8753,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>181</v>
@@ -8443,7 +8776,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>1</v>
@@ -8457,10 +8790,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>183</v>
@@ -8480,10 +8813,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>185</v>
@@ -8503,7 +8836,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -8517,10 +8850,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>187</v>
@@ -8540,10 +8873,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>189</v>
@@ -8563,10 +8896,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>191</v>
@@ -8586,10 +8919,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>193</v>
@@ -8609,10 +8942,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>195</v>
@@ -8637,7 +8970,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>197</v>
@@ -8651,7 +8984,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>199</v>
@@ -8665,7 +8998,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>201</v>
@@ -8679,7 +9012,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>203</v>
@@ -8696,10 +9029,10 @@
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>205</v>
@@ -8740,7 +9073,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>119</v>
@@ -8757,10 +9090,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>207</v>
@@ -8777,10 +9110,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>209</v>
@@ -8797,10 +9130,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>211</v>
@@ -8817,10 +9150,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>213</v>
@@ -8837,7 +9170,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -8848,7 +9181,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -8859,10 +9192,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>215</v>
@@ -8879,10 +9212,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>217</v>
@@ -8899,10 +9232,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>219</v>
@@ -8919,7 +9252,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -8930,10 +9263,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>221</v>
@@ -8950,10 +9283,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>223</v>
@@ -8970,10 +9303,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>225</v>
@@ -8990,10 +9323,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>227</v>
@@ -9010,10 +9343,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>229</v>
@@ -9030,7 +9363,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -9041,10 +9374,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>231</v>
@@ -9061,10 +9394,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>233</v>
@@ -9081,10 +9414,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>235</v>
@@ -9101,10 +9434,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>237</v>
@@ -9121,10 +9454,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>239</v>
@@ -9141,10 +9474,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>241</v>
@@ -9182,7 +9515,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>119</v>
@@ -9194,7 +9527,7 @@
         <v>121</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>122</v>
@@ -9208,7 +9541,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -9219,10 +9552,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>243</v>
@@ -9239,7 +9572,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -9250,10 +9583,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>245</v>
@@ -9270,7 +9603,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -9281,7 +9614,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -9292,10 +9625,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>247</v>
@@ -9312,10 +9645,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>249</v>
@@ -9332,10 +9665,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>251</v>
@@ -9352,7 +9685,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -9363,10 +9696,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>253</v>
@@ -9383,10 +9716,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>255</v>
@@ -9403,7 +9736,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>1</v>
@@ -9414,10 +9747,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>257</v>
@@ -9434,10 +9767,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>259</v>
@@ -9454,7 +9787,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -9465,7 +9798,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>1</v>
@@ -9476,7 +9809,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>1</v>
@@ -9487,10 +9820,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>261</v>
@@ -9507,7 +9840,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>1</v>
@@ -9518,10 +9851,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>263</v>
@@ -9535,7 +9868,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>265</v>
@@ -9552,7 +9885,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>1</v>
@@ -9589,7 +9922,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>119</v>
@@ -9601,7 +9934,7 @@
         <v>164</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>122</v>
@@ -9612,7 +9945,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>267</v>
@@ -9629,7 +9962,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>269</v>
@@ -9646,7 +9979,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>271</v>
@@ -9671,7 +10004,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>273</v>
@@ -9685,7 +10018,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>275</v>
@@ -9699,7 +10032,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>277</v>
@@ -9713,7 +10046,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>279</v>
@@ -9727,7 +10060,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>281</v>
@@ -9741,7 +10074,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>282</v>
@@ -9755,7 +10088,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>284</v>
@@ -9772,7 +10105,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>275</v>
@@ -9789,7 +10122,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>287</v>

--- a/inasistencias-5a-tec-Dig/alumnos-5a-td.xlsx
+++ b/inasistencias-5a-tec-Dig/alumnos-5a-td.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,11 +30,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="326">
   <si>
     <t xml:space="preserve">total</t>
   </si>
   <si>
+    <t xml:space="preserve">Diciembre</t>
+  </si>
+  <si>
     <t xml:space="preserve">nro</t>
   </si>
   <si>
@@ -65,6 +68,9 @@
     <t xml:space="preserve">media</t>
   </si>
   <si>
+    <t xml:space="preserve">nota asistencia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lucila Yanel</t>
   </si>
   <si>
@@ -176,6 +182,9 @@
     <t xml:space="preserve">dimeofrancisco@gmail.com</t>
   </si>
   <si>
+    <t xml:space="preserve">Ausente</t>
+  </si>
+  <si>
     <t xml:space="preserve">Facundo Agustin</t>
   </si>
   <si>
@@ -305,6 +314,9 @@
     <t xml:space="preserve">observaciones</t>
   </si>
   <si>
+    <t xml:space="preserve">Febrero</t>
+  </si>
+  <si>
     <t xml:space="preserve">1-codigo</t>
   </si>
   <si>
@@ -387,6 +399,12 @@
   </si>
   <si>
     <t xml:space="preserve">Aprobo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ausente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprobado</t>
   </si>
   <si>
     <t xml:space="preserve">Finalizado</t>
@@ -1008,7 +1026,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1036,13 +1053,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFEB3B"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC107"/>
-        <bgColor rgb="FFFF9900"/>
+        <bgColor rgb="FFFFBF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -1053,8 +1070,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB3B"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFFBF00"/>
+        <bgColor rgb="FFFFC107"/>
       </patternFill>
     </fill>
   </fills>
@@ -1099,7 +1116,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1148,6 +1165,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1172,6 +1201,30 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1181,11 +1234,10 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="11">
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <color rgb="FF006600"/>
         <sz val="12"/>
@@ -1199,7 +1251,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <color rgb="FFCC0000"/>
         <sz val="12"/>
@@ -1213,7 +1264,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
         <color rgb="FFFFFFFF"/>
@@ -1228,7 +1278,32 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF006600"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="0"/>
+        <color rgb="FFCC0000"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
         <family val="0"/>
         <b val="1"/>
         <color rgb="FFFFFFFF"/>
@@ -1243,7 +1318,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <color rgb="FF006600"/>
         <sz val="12"/>
@@ -1257,7 +1331,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <color rgb="FFCC0000"/>
         <sz val="12"/>
@@ -1266,7 +1339,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
         <color rgb="FFFFFFFF"/>
@@ -1281,7 +1353,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <color rgb="FF006600"/>
         <sz val="12"/>
@@ -1295,7 +1366,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <color rgb="FFCC0000"/>
         <sz val="12"/>
@@ -1335,7 +1405,7 @@
       <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFEB3B"/>
+      <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
@@ -1353,7 +1423,7 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFC107"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
@@ -1481,7 +1551,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AU29"/>
+  <dimension ref="A1:AX29"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
@@ -1491,7 +1561,7 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="11" min="5" style="1" width="8.68"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="12" min="12" style="1" width="12.64"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="22" min="13" style="1" width="8.68"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="42" min="23" style="1" width="8.75"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="42" min="23" style="1" width="8.75"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1512,27 +1582,30 @@
         <v>7</v>
       </c>
       <c r="AR1" s="2"/>
-      <c r="AT1" s="1"/>
       <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>45800</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>45807</v>
@@ -1541,13 +1614,13 @@
         <v>45814</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>45821</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>45835</v>
@@ -1556,31 +1629,31 @@
         <v>45842</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>45849</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W2" s="3" t="n">
         <v>45856</v>
@@ -1589,37 +1662,37 @@
         <v>45898</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z2" s="3" t="n">
         <v>45905</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB2" s="3" t="n">
         <v>45919</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD2" s="3" t="n">
         <v>45926</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF2" s="3" t="n">
         <v>45933</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH2" s="3" t="n">
         <v>45947</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ2" s="3" t="n">
         <v>45954</v>
@@ -1628,59 +1701,75 @@
         <v>45961</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ2" s="3" t="n">
         <v>45996</v>
       </c>
-      <c r="AT2" s="2"/>
-      <c r="AU2" s="2"/>
+      <c r="AR2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AS2" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="AT2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AW2" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P3" s="4" t="n">
         <v>0.520833333333333</v>
@@ -1706,31 +1795,31 @@
         <v>10</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM3" s="2" t="n">
         <f aca="false">COUNTIF(W3:AL3,"p")</f>
@@ -1754,34 +1843,34 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q4" s="1" t="n">
         <f aca="false">COUNTIF(E4:O4,"P")</f>
@@ -1804,31 +1893,31 @@
         <v>10</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ4" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM4" s="2" t="n">
         <f aca="false">COUNTIF(W4:AL4,"p")</f>
@@ -1852,34 +1941,34 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P5" s="4" t="n">
         <v>0.520833333333333</v>
@@ -1905,31 +1994,31 @@
         <v>10</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK5" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM5" s="2" t="n">
         <f aca="false">COUNTIF(W5:AL5,"p")</f>
@@ -1953,34 +2042,34 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P6" s="4" t="n">
         <v>0.53125</v>
@@ -2006,31 +2095,31 @@
         <v>4</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ6" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK6" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM6" s="2" t="n">
         <f aca="false">COUNTIF(W6:AL6,"p")</f>
@@ -2054,40 +2143,40 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="F7" s="4" t="n">
-        <v>0.555555555555555</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>0.527777777777778</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P7" s="4" t="n">
         <v>0.548611111111111</v>
@@ -2113,37 +2202,37 @@
         <v>4</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y7" s="4" t="n">
         <v>0.532638888888889</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE7" s="4" t="n">
         <v>0.572916666666667</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AM7" s="2" t="n">
         <f aca="false">COUNTIF(W7:AL7,"p")</f>
@@ -2162,43 +2251,43 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" s="8" customFormat="true" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P8" s="7"/>
       <c r="Q8" s="7" t="n">
@@ -2223,41 +2312,41 @@
         <v>10</v>
       </c>
       <c r="W8" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X8" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y8" s="7"/>
       <c r="Z8" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>0.517361111111111</v>
       </c>
       <c r="AB8" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AC8" s="7"/>
       <c r="AD8" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE8" s="10" t="n">
         <v>0.520833333333333</v>
       </c>
       <c r="AF8" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AG8" s="7"/>
       <c r="AH8" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI8" s="7"/>
       <c r="AJ8" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK8" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL8" s="7"/>
       <c r="AM8" s="8" t="n">
@@ -2277,7 +2366,10 @@
         <v>5</v>
       </c>
       <c r="AQ8" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="AS8" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2285,37 +2377,37 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0.520833333333333</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q9" s="1" t="n">
         <f aca="false">COUNTIF(E9:O9,"P")</f>
@@ -2338,31 +2430,31 @@
         <v>10</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM9" s="2" t="n">
         <f aca="false">COUNTIF(W9:AL9,"p")</f>
@@ -2386,37 +2478,37 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q10" s="1" t="n">
         <f aca="false">COUNTIF(E10:O10,"P")</f>
@@ -2439,34 +2531,34 @@
         <v>10</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ10" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM10" s="2" t="n">
         <f aca="false">COUNTIF(W10:AL10,"p")</f>
@@ -2490,34 +2582,34 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q11" s="1" t="n">
         <f aca="false">COUNTIF(E11:O11,"P")</f>
@@ -2540,31 +2632,31 @@
         <v>10</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF11" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ11" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK11" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AM11" s="2" t="n">
         <f aca="false">COUNTIF(W11:AL11,"p")</f>
@@ -2583,156 +2675,174 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="8" t="s">
+    <row r="12" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7" t="n">
+      <c r="C12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1" t="n">
         <f aca="false">COUNTIF(E12:O12,"P")</f>
         <v>7</v>
       </c>
-      <c r="R12" s="7" t="n">
+      <c r="R12" s="1" t="n">
         <f aca="false">COUNTIF(E12:O12,"M")</f>
         <v>0</v>
       </c>
-      <c r="S12" s="7" t="n">
+      <c r="S12" s="1" t="n">
         <f aca="false">COUNTIF(E12:O12,"T")</f>
         <v>0</v>
       </c>
-      <c r="T12" s="7" t="n">
+      <c r="T12" s="1" t="n">
         <f aca="false">ROUND(Q12+R12/2+S12/4,0)</f>
         <v>7</v>
       </c>
-      <c r="U12" s="7"/>
-      <c r="V12" s="9" t="n">
+      <c r="U12" s="1"/>
+      <c r="V12" s="5" t="n">
         <f aca="false">ROUND(T12*10/$W$1,0)</f>
         <v>10</v>
       </c>
-      <c r="W12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="X12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA12" s="7"/>
-      <c r="AB12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC12" s="7"/>
-      <c r="AD12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE12" s="7"/>
-      <c r="AF12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG12" s="7"/>
-      <c r="AH12" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI12" s="7"/>
-      <c r="AJ12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL12" s="7"/>
-      <c r="AM12" s="8" t="n">
+      <c r="W12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC12" s="1"/>
+      <c r="AD12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG12" s="1"/>
+      <c r="AH12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI12" s="1"/>
+      <c r="AJ12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL12" s="1"/>
+      <c r="AM12" s="2" t="n">
         <f aca="false">COUNTIF(W12:AL12,"p")</f>
         <v>6</v>
       </c>
-      <c r="AN12" s="8" t="n">
+      <c r="AN12" s="2" t="n">
         <f aca="false">COUNTIF(W12:AL12,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO12" s="8" t="n">
+      <c r="AO12" s="2" t="n">
         <f aca="false">COUNTIF(W12:AL12,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP12" s="11" t="n">
+      <c r="AP12" s="6" t="n">
         <f aca="false">ROUND((AM12+AN12/2+AO12/4)*10/9,0)</f>
         <v>7</v>
       </c>
-      <c r="AQ12" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AQ12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AS12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AU12" s="2" t="n">
+        <f aca="false">COUNTIF(AQ12:AS12,"P")</f>
+        <v>0</v>
+      </c>
+      <c r="AV12" s="2" t="n">
+        <f aca="false">COUNTIF(AQ12:AS12,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AW12" s="12" t="n">
+        <f aca="false">(AU12+AV12/4)*5</f>
+        <v>0</v>
+      </c>
+      <c r="AX12" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="true" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q13" s="1" t="n">
         <f aca="false">COUNTIF(E13:O13,"P")</f>
@@ -2755,37 +2865,37 @@
         <v>10</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE13" s="4" t="n">
         <v>0.520833333333333</v>
       </c>
       <c r="AF13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ13" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK13" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM13" s="2" t="n">
         <f aca="false">COUNTIF(W13:AL13,"p")</f>
@@ -2804,39 +2914,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" s="1" customFormat="true" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q14" s="1" t="n">
         <f aca="false">COUNTIF(E14:O14,"P")</f>
@@ -2859,31 +2969,31 @@
         <v>9</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD14" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF14" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ14" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK14" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM14" s="2" t="n">
         <f aca="false">COUNTIF(W14:AL14,"p")</f>
@@ -2902,153 +3012,168 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
+    <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7" t="n">
+      <c r="B15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1" t="n">
         <f aca="false">COUNTIF(E15:O15,"P")</f>
         <v>6</v>
       </c>
-      <c r="R15" s="7" t="n">
+      <c r="R15" s="1" t="n">
         <f aca="false">COUNTIF(E15:O15,"M")</f>
         <v>0</v>
       </c>
-      <c r="S15" s="7" t="n">
+      <c r="S15" s="1" t="n">
         <f aca="false">COUNTIF(E15:O15,"T")</f>
         <v>0</v>
       </c>
-      <c r="T15" s="7" t="n">
+      <c r="T15" s="1" t="n">
         <f aca="false">ROUND(Q15+R15/2+S15/4,0)</f>
         <v>6</v>
       </c>
-      <c r="U15" s="7"/>
-      <c r="V15" s="9" t="n">
+      <c r="U15" s="1"/>
+      <c r="V15" s="5" t="n">
         <f aca="false">ROUND(T15*10/$W$1,0)</f>
         <v>9</v>
       </c>
-      <c r="W15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="X15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA15" s="7"/>
-      <c r="AB15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC15" s="7"/>
-      <c r="AD15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE15" s="7"/>
-      <c r="AF15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG15" s="7"/>
-      <c r="AH15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI15" s="7"/>
-      <c r="AJ15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL15" s="7"/>
-      <c r="AM15" s="8" t="n">
+      <c r="W15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC15" s="1"/>
+      <c r="AD15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE15" s="1"/>
+      <c r="AF15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG15" s="1"/>
+      <c r="AH15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI15" s="1"/>
+      <c r="AJ15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL15" s="1"/>
+      <c r="AM15" s="2" t="n">
         <f aca="false">COUNTIF(W15:AL15,"p")</f>
         <v>8</v>
       </c>
-      <c r="AN15" s="8" t="n">
+      <c r="AN15" s="2" t="n">
         <f aca="false">COUNTIF(W15:AL15,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO15" s="8" t="n">
+      <c r="AO15" s="2" t="n">
         <f aca="false">COUNTIF(W15:AL15,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP15" s="11" t="n">
+      <c r="AP15" s="6" t="n">
         <f aca="false">ROUND((AM15+AN15/2+AO15/4)*10/9,0)</f>
         <v>9</v>
       </c>
-      <c r="AQ15" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AQ15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU15" s="2" t="n">
+        <f aca="false">COUNTIF(AQ15:AS15,"P")</f>
+        <v>2</v>
+      </c>
+      <c r="AV15" s="2" t="n">
+        <f aca="false">COUNTIF(AQ15:AS15,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AW15" s="12" t="n">
+        <f aca="false">(AU15+AV15/4)*5</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="true" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q16" s="1" t="n">
         <f aca="false">COUNTIF(E16:O16,"P")</f>
@@ -3071,31 +3196,31 @@
         <v>7</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ16" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK16" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM16" s="2" t="n">
         <f aca="false">COUNTIF(W16:AL16,"p")</f>
@@ -3114,39 +3239,39 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="1" customFormat="true" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q17" s="1" t="n">
         <f aca="false">COUNTIF(E17:O17,"P")</f>
@@ -3169,31 +3294,31 @@
         <v>10</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD17" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ17" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK17" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AM17" s="2" t="n">
         <f aca="false">COUNTIF(W17:AL17,"p")</f>
@@ -3212,392 +3337,443 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" s="10" t="n">
+    <row r="18" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18" s="4" t="n">
         <v>0.541666666666667</v>
       </c>
-      <c r="L18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7" t="n">
+      <c r="L18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1" t="n">
         <f aca="false">COUNTIF(E18:O18,"P")</f>
         <v>5</v>
       </c>
-      <c r="R18" s="7" t="n">
+      <c r="R18" s="1" t="n">
         <f aca="false">COUNTIF(E18:O18,"M")</f>
         <v>0</v>
       </c>
-      <c r="S18" s="7" t="n">
+      <c r="S18" s="1" t="n">
         <f aca="false">COUNTIF(E18:O18,"T")</f>
         <v>1</v>
       </c>
-      <c r="T18" s="7" t="n">
+      <c r="T18" s="1" t="n">
         <f aca="false">ROUND(Q18+R18/2+S18/4,0)</f>
         <v>5</v>
       </c>
-      <c r="U18" s="7"/>
-      <c r="V18" s="9" t="n">
+      <c r="U18" s="1"/>
+      <c r="V18" s="5" t="n">
         <f aca="false">ROUND(T18*10/$W$1,0)</f>
         <v>7</v>
       </c>
-      <c r="W18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="X18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA18" s="7"/>
-      <c r="AB18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC18" s="7"/>
-      <c r="AD18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE18" s="10" t="n">
+      <c r="W18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC18" s="1"/>
+      <c r="AD18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE18" s="4" t="n">
         <v>0.520833333333333</v>
       </c>
-      <c r="AF18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG18" s="10" t="n">
+      <c r="AF18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG18" s="4" t="n">
         <v>0.545138888888889</v>
       </c>
-      <c r="AH18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI18" s="7"/>
-      <c r="AJ18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL18" s="7"/>
-      <c r="AM18" s="8" t="n">
+      <c r="AH18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI18" s="1"/>
+      <c r="AJ18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL18" s="1"/>
+      <c r="AM18" s="2" t="n">
         <f aca="false">COUNTIF(W18:AL18,"p")</f>
         <v>1</v>
       </c>
-      <c r="AN18" s="8" t="n">
+      <c r="AN18" s="2" t="n">
         <f aca="false">COUNTIF(W18:AL18,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO18" s="8" t="n">
+      <c r="AO18" s="2" t="n">
         <f aca="false">COUNTIF(W18:AL18,"T")</f>
         <v>2</v>
       </c>
-      <c r="AP18" s="11" t="n">
+      <c r="AP18" s="6" t="n">
         <f aca="false">ROUND((AM18+AN18/2+AO18/4)*10/9,0)</f>
         <v>2</v>
       </c>
-      <c r="AQ18" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="AR18" s="10" t="n">
+      <c r="AQ18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AR18" s="4" t="n">
         <v>0.583333333333333</v>
       </c>
-    </row>
-    <row r="19" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
+      <c r="AS18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AT18" s="13" t="n">
+        <v>0.555555555555556</v>
+      </c>
+      <c r="AU18" s="2" t="n">
+        <f aca="false">COUNTIF(AQ18:AS18,"P")</f>
+        <v>0</v>
+      </c>
+      <c r="AV18" s="2" t="n">
+        <f aca="false">COUNTIF(AQ18:AS18,"T")</f>
+        <v>2</v>
+      </c>
+      <c r="AW18" s="12" t="n">
+        <f aca="false">(AU18+AV18/4)*5</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7" t="n">
+      <c r="B19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1" t="n">
         <f aca="false">COUNTIF(E19:O19,"P")</f>
         <v>6</v>
       </c>
-      <c r="R19" s="7" t="n">
+      <c r="R19" s="1" t="n">
         <f aca="false">COUNTIF(E19:O19,"M")</f>
         <v>0</v>
       </c>
-      <c r="S19" s="7" t="n">
+      <c r="S19" s="1" t="n">
         <f aca="false">COUNTIF(E19:O19,"T")</f>
         <v>0</v>
       </c>
-      <c r="T19" s="7" t="n">
+      <c r="T19" s="1" t="n">
         <f aca="false">ROUND(Q19+R19/2+S19/4,0)</f>
         <v>6</v>
       </c>
-      <c r="U19" s="7"/>
-      <c r="V19" s="9" t="n">
+      <c r="U19" s="1"/>
+      <c r="V19" s="5" t="n">
         <f aca="false">ROUND(T19*10/$W$1,0)</f>
         <v>9</v>
       </c>
-      <c r="W19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="X19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA19" s="7"/>
-      <c r="AB19" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC19" s="7"/>
-      <c r="AD19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE19" s="7"/>
-      <c r="AF19" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG19" s="7"/>
-      <c r="AH19" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI19" s="7"/>
-      <c r="AJ19" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK19" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL19" s="7"/>
-      <c r="AM19" s="8" t="n">
+      <c r="W19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC19" s="1"/>
+      <c r="AD19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG19" s="1"/>
+      <c r="AH19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI19" s="1"/>
+      <c r="AJ19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL19" s="1"/>
+      <c r="AM19" s="2" t="n">
         <f aca="false">COUNTIF(W19:AL19,"p")</f>
         <v>6</v>
       </c>
-      <c r="AN19" s="8" t="n">
+      <c r="AN19" s="2" t="n">
         <f aca="false">COUNTIF(W19:AL19,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO19" s="8" t="n">
+      <c r="AO19" s="2" t="n">
         <f aca="false">COUNTIF(W19:AL19,"T")</f>
         <v>0</v>
       </c>
-      <c r="AP19" s="11" t="n">
+      <c r="AP19" s="6" t="n">
         <f aca="false">ROUND((AM19+AN19/2+AO19/4)*10/9,0)</f>
         <v>7</v>
       </c>
-      <c r="AQ19" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="n">
+      <c r="AQ19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU19" s="2" t="n">
+        <f aca="false">COUNTIF(AQ19:AS19,"P")</f>
+        <v>2</v>
+      </c>
+      <c r="AV19" s="2" t="n">
+        <f aca="false">COUNTIF(AQ19:AS19,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AW19" s="12" t="n">
+        <f aca="false">(AU19+AV19/4)*5</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" s="10" t="n">
+      <c r="B20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="4" t="n">
         <v>0.527777777777778</v>
       </c>
-      <c r="J20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7" t="n">
+      <c r="J20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1" t="n">
         <f aca="false">COUNTIF(E20:O20,"P")</f>
         <v>4</v>
       </c>
-      <c r="R20" s="7" t="n">
+      <c r="R20" s="1" t="n">
         <f aca="false">COUNTIF(E20:O20,"M")</f>
         <v>0</v>
       </c>
-      <c r="S20" s="7" t="n">
+      <c r="S20" s="1" t="n">
         <f aca="false">COUNTIF(E20:O20,"T")</f>
         <v>1</v>
       </c>
-      <c r="T20" s="7" t="n">
+      <c r="T20" s="1" t="n">
         <f aca="false">ROUND(Q20+R20/2+S20/4,0)</f>
         <v>4</v>
       </c>
-      <c r="U20" s="7"/>
-      <c r="V20" s="9" t="n">
+      <c r="U20" s="1"/>
+      <c r="V20" s="5" t="n">
         <f aca="false">ROUND(T20*10/$W$1,0)</f>
         <v>6</v>
       </c>
-      <c r="W20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="X20" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y20" s="7"/>
-      <c r="Z20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA20" s="7"/>
-      <c r="AB20" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC20" s="7"/>
-      <c r="AD20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE20" s="7"/>
-      <c r="AF20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG20" s="7"/>
-      <c r="AH20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI20" s="7"/>
-      <c r="AJ20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK20" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL20" s="7"/>
-      <c r="AM20" s="8" t="n">
+      <c r="W20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC20" s="1"/>
+      <c r="AD20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE20" s="1"/>
+      <c r="AF20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG20" s="1"/>
+      <c r="AH20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI20" s="1"/>
+      <c r="AJ20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL20" s="1"/>
+      <c r="AM20" s="2" t="n">
         <f aca="false">COUNTIF(W20:AL20,"p")</f>
         <v>6</v>
       </c>
-      <c r="AN20" s="8" t="n">
+      <c r="AN20" s="2" t="n">
         <f aca="false">COUNTIF(W20:AL20,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO20" s="8" t="n">
+      <c r="AO20" s="2" t="n">
         <f aca="false">COUNTIF(W20:AL20,"T")</f>
         <v>1</v>
       </c>
-      <c r="AP20" s="11" t="n">
+      <c r="AP20" s="6" t="n">
         <f aca="false">ROUND((AM20+AN20/2+AO20/4)*10/9,0)</f>
         <v>7</v>
       </c>
-      <c r="AQ20" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AQ20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AS20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AU20" s="2" t="n">
+        <f aca="false">COUNTIF(AQ20:AS20,"P")</f>
+        <v>0</v>
+      </c>
+      <c r="AV20" s="2" t="n">
+        <f aca="false">COUNTIF(AQ20:AS20,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AW20" s="12" t="n">
+        <f aca="false">(AU20+AV20/4)*5</f>
+        <v>0</v>
+      </c>
+      <c r="AX20" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="true" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q21" s="1" t="n">
         <f aca="false">COUNTIF(E21:O21,"P")</f>
@@ -3620,31 +3796,31 @@
         <v>9</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AD21" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AF21" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AJ21" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AK21" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AM21" s="2" t="n">
         <f aca="false">COUNTIF(W21:AL21,"p")</f>
@@ -3663,39 +3839,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" s="1" customFormat="true" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q22" s="1" t="n">
         <f aca="false">COUNTIF(E22:O22,"P")</f>
@@ -3718,31 +3894,31 @@
         <v>10</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF22" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH22" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ22" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK22" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM22" s="2" t="n">
         <f aca="false">COUNTIF(W22:AL22,"p")</f>
@@ -3761,45 +3937,45 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" s="1" customFormat="true" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0.520833333333333</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>0.520833333333333</v>
@@ -3825,34 +4001,34 @@
         <v>6</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA23" s="4" t="n">
         <v>0.517361111111111</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD23" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF23" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ23" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK23" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL23" s="4" t="n">
         <v>0.53125</v>
@@ -3874,128 +4050,143 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
+    <row r="24" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7" t="n">
+      <c r="B24" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1" t="n">
         <f aca="false">COUNTIF(E24:O24,"P")</f>
         <v>7</v>
       </c>
-      <c r="R24" s="7" t="n">
+      <c r="R24" s="1" t="n">
         <f aca="false">COUNTIF(E24:O24,"M")</f>
         <v>0</v>
       </c>
-      <c r="S24" s="7" t="n">
+      <c r="S24" s="1" t="n">
         <f aca="false">COUNTIF(E24:O24,"T")</f>
         <v>0</v>
       </c>
-      <c r="T24" s="7" t="n">
+      <c r="T24" s="1" t="n">
         <f aca="false">ROUND(Q24+R24/2+S24/4,0)</f>
         <v>7</v>
       </c>
-      <c r="U24" s="7"/>
-      <c r="V24" s="9" t="n">
+      <c r="U24" s="1"/>
+      <c r="V24" s="5" t="n">
         <f aca="false">ROUND(T24*10/$W$1,0)</f>
         <v>10</v>
       </c>
-      <c r="W24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="X24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y24" s="7"/>
-      <c r="Z24" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA24" s="7"/>
-      <c r="AB24" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC24" s="10" t="n">
+      <c r="W24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC24" s="4" t="n">
         <v>0.538194444444444</v>
       </c>
-      <c r="AD24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE24" s="7"/>
-      <c r="AF24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG24" s="7"/>
-      <c r="AH24" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI24" s="7"/>
-      <c r="AJ24" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK24" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL24" s="7"/>
-      <c r="AM24" s="8" t="n">
+      <c r="AD24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG24" s="1"/>
+      <c r="AH24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI24" s="1"/>
+      <c r="AJ24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL24" s="1"/>
+      <c r="AM24" s="2" t="n">
         <f aca="false">COUNTIF(W24:AL24,"p")</f>
         <v>6</v>
       </c>
-      <c r="AN24" s="8" t="n">
+      <c r="AN24" s="2" t="n">
         <f aca="false">COUNTIF(W24:AL24,"M")</f>
         <v>0</v>
       </c>
-      <c r="AO24" s="8" t="n">
+      <c r="AO24" s="2" t="n">
         <f aca="false">COUNTIF(W24:AL24,"T")</f>
         <v>1</v>
       </c>
-      <c r="AP24" s="11" t="n">
+      <c r="AP24" s="6" t="n">
         <f aca="false">ROUND((AM24+AN24/2+AO24/4)*10/9,0)</f>
         <v>7</v>
       </c>
-      <c r="AQ24" s="8" t="s">
-        <v>14</v>
+      <c r="AQ24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU24" s="2" t="n">
+        <f aca="false">COUNTIF(AQ24:AS24,"P")</f>
+        <v>2</v>
+      </c>
+      <c r="AV24" s="2" t="n">
+        <f aca="false">COUNTIF(AQ24:AS24,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AW24" s="12" t="n">
+        <f aca="false">(AU24+AV24/4)*5</f>
+        <v>10</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25" s="1" t="n">
         <f aca="false">COUNTIF(E3:E24,"P")</f>
@@ -4065,10 +4256,15 @@
         <f aca="false">COUNTIF(AQ8:AQ24,"P")</f>
         <v>4</v>
       </c>
+      <c r="AS25" s="1" t="n">
+        <f aca="false">COUNTIF(AS8:AS24,"P")</f>
+        <v>3</v>
+      </c>
+      <c r="AT25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="X26" s="1" t="n">
         <f aca="false">COUNTIF(X3:X24,"M")</f>
@@ -4105,7 +4301,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X27" s="1" t="n">
         <f aca="false">COUNTIF(X3:X24,"T")</f>
@@ -4142,7 +4338,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF28" s="1" t="n">
         <f aca="false">COUNTIF(AF3:AF24,"o")</f>
@@ -4163,7 +4359,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="X29" s="1" t="n">
         <f aca="false">SUM(X25:X27)</f>
@@ -4209,6 +4405,14 @@
     </cfRule>
     <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AW12:AW24">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4237,25 +4441,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4263,7 +4467,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -4277,16 +4481,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8</v>
@@ -4300,7 +4504,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -4314,16 +4518,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>8</v>
@@ -4337,7 +4541,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -4351,7 +4555,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -4365,16 +4569,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>6</v>
@@ -4388,16 +4592,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -4416,13 +4620,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>9</v>
@@ -4433,16 +4637,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>7</v>
@@ -4461,13 +4665,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>6</v>
@@ -4478,7 +4682,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>1</v>
@@ -4492,16 +4696,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -4515,16 +4719,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9</v>
@@ -4538,7 +4742,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -4552,16 +4756,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>6</v>
@@ -4575,7 +4779,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>1</v>
@@ -4589,7 +4793,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>1</v>
@@ -4603,7 +4807,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>1</v>
@@ -4617,7 +4821,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>1</v>
@@ -4631,7 +4835,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>1</v>
@@ -4645,7 +4849,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>1</v>
@@ -4659,16 +4863,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>7</v>
@@ -4687,13 +4891,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>5</v>
@@ -4701,13 +4905,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>5</v>
@@ -4718,7 +4922,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>1</v>
@@ -4767,16 +4971,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4784,16 +4988,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>8.5</v>
@@ -4804,16 +5008,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>7</v>
@@ -4824,16 +5028,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -4844,16 +5048,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>9</v>
@@ -4864,7 +5068,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -4875,16 +5079,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -4895,16 +5099,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>8.75</v>
@@ -4915,16 +5119,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -4935,16 +5139,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8.75</v>
@@ -4955,16 +5159,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>8.25</v>
@@ -4975,16 +5179,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8.75</v>
@@ -4995,16 +5199,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9.5</v>
@@ -5015,16 +5219,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>7.25</v>
@@ -5035,16 +5239,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9.25</v>
@@ -5055,16 +5259,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>7.25</v>
@@ -5075,7 +5279,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -5086,16 +5290,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>9</v>
@@ -5106,16 +5310,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8.5</v>
@@ -5126,16 +5330,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8.5</v>
@@ -5146,16 +5350,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -5166,16 +5370,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9.25</v>
@@ -5186,16 +5390,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -5224,18 +5428,19 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="3" style="1" width="9.36"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="14" style="1" width="9.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="9.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="19.39"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="32" min="22" style="1" width="9.56"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="39" min="33" style="1" width="9.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="14.12"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="20" min="20" style="1" width="9.56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="21" min="21" style="1" width="19.39"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="32" min="22" style="1" width="9.56"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="42" min="33" style="1" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="43" min="43" style="1" width="14.12"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="44" min="44" style="0" width="9.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1027" min="1027" style="1" width="9.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="2"/>
       <c r="T1" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="V1" s="3"/>
       <c r="AI1" s="2"/>
@@ -5244,150 +5449,159 @@
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
       <c r="AN1" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AO1" s="2"/>
       <c r="AP1" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ1" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AR1" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
+      </c>
+      <c r="AS1" s="0" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="S2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="U2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V2" s="3" t="n">
         <v>45877</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="AA2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="AC2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="AK2" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AP2" s="2"/>
       <c r="AQ2" s="2"/>
       <c r="AR2" s="2"/>
+      <c r="AS2" s="14" t="n">
+        <v>46080</v>
+      </c>
+      <c r="AT2" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>10</v>
@@ -5419,10 +5633,10 @@
         <f aca="false">IF(M3&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O3" s="12" t="n">
+      <c r="O3" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="P3" s="13" t="n">
+      <c r="P3" s="16" t="n">
         <v>45783</v>
       </c>
       <c r="Q3" s="1" t="n">
@@ -5431,7 +5645,7 @@
       <c r="S3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="T3" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S3,Q3,O3,M3),0)</f>
         <v>8</v>
       </c>
@@ -5474,7 +5688,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>10</v>
@@ -5512,7 +5726,7 @@
       <c r="S4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="T4" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S4,Q4,O4,M4),0)</f>
         <v>9</v>
       </c>
@@ -5555,7 +5769,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>9</v>
@@ -5587,10 +5801,10 @@
         <f aca="false">IF(M5&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O5" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="P5" s="13" t="n">
+      <c r="O5" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="P5" s="16" t="n">
         <v>45782</v>
       </c>
       <c r="Q5" s="1" t="n">
@@ -5599,7 +5813,7 @@
       <c r="S5" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="T5" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S5,Q5,O5,M5),0)</f>
         <v>9</v>
       </c>
@@ -5639,7 +5853,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>10</v>
@@ -5677,7 +5891,7 @@
       <c r="S6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="T6" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S6,Q6,O6,M6),0)</f>
         <v>8</v>
       </c>
@@ -5717,7 +5931,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>9</v>
@@ -5729,16 +5943,16 @@
         <v>9</v>
       </c>
       <c r="F7" s="7"/>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="16" t="n">
         <v>45875</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="16" t="n">
         <v>45875</v>
       </c>
       <c r="K7" s="1" t="n">
@@ -5756,10 +5970,10 @@
         <f aca="false">IF(M7&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O7" s="12" t="n">
+      <c r="O7" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="P7" s="13" t="n">
+      <c r="P7" s="16" t="n">
         <v>45875</v>
       </c>
       <c r="Q7" s="1" t="n">
@@ -5771,15 +5985,15 @@
       <c r="S7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="T7" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S7,Q7,O7,M7),0)</f>
         <v>7</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AC7" s="1" t="n">
         <v>1</v>
@@ -5812,17 +6026,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" s="8" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" s="8" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="17" t="n">
         <v>45842</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -5836,7 +6050,7 @@
       <c r="I8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J8" s="17" t="n">
         <v>45784</v>
       </c>
       <c r="K8" s="7" t="n">
@@ -5857,7 +6071,7 @@
       <c r="O8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="P8" s="14" t="n">
+      <c r="P8" s="17" t="n">
         <v>45784</v>
       </c>
       <c r="Q8" s="7" t="n">
@@ -5885,18 +6099,18 @@
       <c r="Z8" s="7"/>
       <c r="AA8" s="7"/>
       <c r="AB8" s="7"/>
-      <c r="AC8" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD8" s="16" t="n">
+      <c r="AC8" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD8" s="19" t="n">
         <v>45996</v>
       </c>
       <c r="AE8" s="7"/>
       <c r="AF8" s="7"/>
-      <c r="AG8" s="15" t="n">
+      <c r="AG8" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="AH8" s="16" t="n">
+      <c r="AH8" s="19" t="n">
         <v>45996</v>
       </c>
       <c r="AI8" s="7" t="n">
@@ -5926,12 +6140,11 @@
         <f aca="false">ROUND(AVERAGE(AC8,AG8,AI8,AJ8),0)</f>
         <v>9</v>
       </c>
-      <c r="AQ8" s="11" t="n">
-        <f aca="false">ROUND(AP8*6/10,0)</f>
-        <v>5</v>
+      <c r="AQ8" s="7" t="n">
+        <v>10</v>
       </c>
       <c r="AR8" s="8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="AMM8" s="7"/>
     </row>
@@ -5940,7 +6153,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>10</v>
@@ -5978,7 +6191,7 @@
       <c r="S9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="T9" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S9,Q9,O9,M9),0)</f>
         <v>9</v>
       </c>
@@ -6018,7 +6231,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>9</v>
@@ -6056,7 +6269,7 @@
       <c r="S10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="T10" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S10,Q10,O10,M10),0)</f>
         <v>10</v>
       </c>
@@ -6096,7 +6309,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>10</v>
@@ -6134,7 +6347,7 @@
       <c r="S11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="T11" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S11,Q11,O11,M11),0)</f>
         <v>9</v>
       </c>
@@ -6169,119 +6382,131 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="8" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7" t="n">
+    <row r="12" s="21" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>46073</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="20"/>
+      <c r="G12" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" s="22" t="n">
+        <v>46080</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="L12" s="20" t="n">
         <f aca="false">I12+K12/2</f>
         <v>2.5</v>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="20" t="n">
         <f aca="false">ROUND(AVERAGE(C12,E12,G12,L12),0)</f>
-        <v>1</v>
-      </c>
-      <c r="N12" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="N12" s="23" t="str">
         <f aca="false">IF(M12&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="O12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7" t="n">
+      <c r="O12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20" t="n">
         <v>8.25</v>
       </c>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" s="11" t="n">
+      <c r="R12" s="20"/>
+      <c r="S12" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" s="23" t="n">
         <f aca="false">ROUND(AVERAGE(S12,Q12,O12,M12),0)</f>
-        <v>5</v>
-      </c>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
-      <c r="AA12" s="7"/>
-      <c r="AB12" s="7"/>
-      <c r="AC12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD12" s="7"/>
-      <c r="AE12" s="7"/>
-      <c r="AF12" s="7"/>
-      <c r="AG12" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="20"/>
+      <c r="AE12" s="20"/>
+      <c r="AF12" s="20"/>
+      <c r="AG12" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="AH12" s="7"/>
-      <c r="AI12" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ12" s="7" t="n">
+      <c r="AH12" s="20"/>
+      <c r="AI12" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ12" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="AK12" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="8" t="n">
+      <c r="AK12" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="21" t="n">
         <f aca="false">AK12+AL12/2</f>
         <v>7</v>
       </c>
-      <c r="AN12" s="11" t="n">
+      <c r="AN12" s="23" t="n">
         <f aca="false">ROUND(AVERAGE(AG12,AI12,AJ12,AM12),0)</f>
         <v>6</v>
       </c>
-      <c r="AO12" s="7" t="n">
+      <c r="AO12" s="23" t="n">
         <f aca="false">ROUND(AVERAGE(T12,AN12),0)</f>
         <v>6</v>
       </c>
-      <c r="AP12" s="8" t="n">
+      <c r="AP12" s="21" t="n">
         <f aca="false">ROUND(AVERAGE(AC12,AG12,AI12,AJ12),0)</f>
         <v>5</v>
       </c>
-      <c r="AQ12" s="11" t="n">
-        <f aca="false">ROUND(AP12*6/10,0)</f>
-        <v>3</v>
-      </c>
-      <c r="AMM12" s="7"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AQ12" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR12" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="AS12" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT12" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="AMM12" s="20"/>
+    </row>
+    <row r="13" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>10</v>
@@ -6319,7 +6544,7 @@
       <c r="S13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="T13" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S13,Q13,O13,M13),0)</f>
         <v>10</v>
       </c>
@@ -6354,12 +6579,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>7</v>
@@ -6397,7 +6622,7 @@
       <c r="S14" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="T14" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S14,Q14,O14,M14),0)</f>
         <v>9</v>
       </c>
@@ -6432,127 +6657,129 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" s="8" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
+    <row r="15" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7" t="n">
+      <c r="B15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="3" t="n">
         <v>45877</v>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7" t="n">
+      <c r="G15" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J15" s="14" t="n">
+      <c r="J15" s="3" t="n">
         <v>45877</v>
       </c>
-      <c r="K15" s="7" t="n">
+      <c r="K15" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="7" t="n">
+      <c r="L15" s="1" t="n">
         <f aca="false">I15+K15/2</f>
         <v>5.5</v>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="M15" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C15,E15,G15,L15),0)</f>
         <v>7</v>
       </c>
-      <c r="N15" s="11" t="str">
+      <c r="N15" s="6" t="str">
         <f aca="false">IF(M15&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O15" s="7" t="n">
+      <c r="O15" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="P15" s="14" t="n">
+      <c r="P15" s="3" t="n">
         <v>45877</v>
       </c>
-      <c r="Q15" s="7" t="n">
+      <c r="Q15" s="1" t="n">
         <v>7.25</v>
       </c>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="T15" s="11" t="n">
+      <c r="R15" s="1"/>
+      <c r="S15" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T15" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S15,Q15,O15,M15),0)</f>
         <v>7</v>
       </c>
-      <c r="U15" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="V15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
-      <c r="AA15" s="7"/>
-      <c r="AB15" s="7"/>
-      <c r="AC15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD15" s="7"/>
-      <c r="AE15" s="7"/>
-      <c r="AF15" s="7"/>
-      <c r="AG15" s="7" t="n">
+      <c r="U15" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="1"/>
+      <c r="AE15" s="1"/>
+      <c r="AF15" s="1"/>
+      <c r="AG15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AH15" s="7"/>
-      <c r="AI15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK15" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AL15" s="7" t="n">
+      <c r="AH15" s="1"/>
+      <c r="AI15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK15" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL15" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AM15" s="8" t="n">
+      <c r="AM15" s="2" t="n">
         <f aca="false">AK15+AL15/2</f>
         <v>10</v>
       </c>
-      <c r="AN15" s="11" t="n">
+      <c r="AN15" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(AG15,AI15,AJ15,AM15),0)</f>
         <v>5</v>
       </c>
-      <c r="AO15" s="7" t="n">
+      <c r="AO15" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(T15,AN15),0)</f>
         <v>6</v>
       </c>
-      <c r="AP15" s="8" t="n">
+      <c r="AP15" s="2" t="n">
         <f aca="false">ROUND(AVERAGE(AC15,AG15,AI15,AJ15),0)</f>
         <v>3</v>
       </c>
-      <c r="AQ15" s="11" t="n">
-        <f aca="false">ROUND(AP15*6/10,0)</f>
-        <v>2</v>
-      </c>
-      <c r="AMM15" s="7"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AQ15" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR15" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AMM15" s="1"/>
+    </row>
+    <row r="16" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>9</v>
@@ -6590,7 +6817,7 @@
       <c r="S16" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="T16" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S16,Q16,O16,M16),0)</f>
         <v>8</v>
       </c>
@@ -6625,12 +6852,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>10</v>
@@ -6641,7 +6868,7 @@
       <c r="G17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J17" s="3" t="n">
@@ -6662,10 +6889,10 @@
         <f aca="false">IF(M17&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O17" s="12" t="n">
+      <c r="O17" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="P17" s="13" t="n">
+      <c r="P17" s="3" t="n">
         <v>45782</v>
       </c>
       <c r="Q17" s="1" t="n">
@@ -6674,7 +6901,7 @@
       <c r="S17" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="T17" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S17,Q17,O17,M17),0)</f>
         <v>8</v>
       </c>
@@ -6709,388 +6936,404 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" s="8" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D18" s="14" t="n">
+    <row r="18" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>45877</v>
       </c>
-      <c r="E18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="7" t="n">
+      <c r="E18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1" t="n">
         <f aca="false">I18+K18/2</f>
         <v>1</v>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C18,E18,G18,L18),0)</f>
         <v>3</v>
       </c>
-      <c r="N18" s="11" t="str">
+      <c r="N18" s="6" t="str">
         <f aca="false">IF(M18&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="O18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="T18" s="11" t="n">
+      <c r="O18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S18,Q18,O18,M18),0)</f>
         <v>3</v>
       </c>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="7"/>
-      <c r="AB18" s="7"/>
-      <c r="AC18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD18" s="7"/>
-      <c r="AE18" s="7"/>
-      <c r="AF18" s="7"/>
-      <c r="AG18" s="7" t="n">
+      <c r="U18" s="1"/>
+      <c r="V18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1"/>
+      <c r="AC18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="1"/>
+      <c r="AE18" s="1"/>
+      <c r="AF18" s="1"/>
+      <c r="AG18" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AH18" s="7"/>
-      <c r="AI18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK18" s="7" t="n">
+      <c r="AH18" s="1"/>
+      <c r="AI18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AL18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" s="8" t="n">
+      <c r="AL18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="2" t="n">
         <f aca="false">AK18+AL18/2</f>
         <v>2</v>
       </c>
-      <c r="AN18" s="11" t="n">
+      <c r="AN18" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(AG18,AI18,AJ18,AM18),0)</f>
         <v>2</v>
       </c>
-      <c r="AO18" s="7" t="n">
+      <c r="AO18" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(T18,AN18),0)</f>
         <v>3</v>
       </c>
-      <c r="AP18" s="8" t="n">
+      <c r="AP18" s="2" t="n">
         <f aca="false">ROUND(AVERAGE(AC18,AG18,AI18,AJ18),0)</f>
         <v>2</v>
       </c>
-      <c r="AQ18" s="11" t="n">
-        <f aca="false">ROUND(AP18*6/10,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AMM18" s="7"/>
-    </row>
-    <row r="19" s="8" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
+      <c r="AQ18" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR18" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AMM18" s="1"/>
+    </row>
+    <row r="19" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7" t="n">
+      <c r="B19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7" t="n">
+      <c r="H19" s="1"/>
+      <c r="I19" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="J19" s="14" t="n">
+      <c r="J19" s="3" t="n">
         <v>45784</v>
       </c>
-      <c r="K19" s="7" t="n">
+      <c r="K19" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L19" s="7" t="n">
+      <c r="L19" s="1" t="n">
         <f aca="false">I19+K19/2</f>
         <v>7.5</v>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="M19" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C19,E19,G19,L19),0)</f>
         <v>9</v>
       </c>
-      <c r="N19" s="11" t="str">
+      <c r="N19" s="6" t="str">
         <f aca="false">IF(M19&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="T19" s="11" t="n">
+      <c r="O19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="T19" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S19,Q19,O19,M19),0)</f>
         <v>7</v>
       </c>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="7"/>
-      <c r="AA19" s="7"/>
-      <c r="AB19" s="7"/>
-      <c r="AC19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD19" s="7"/>
-      <c r="AE19" s="7"/>
-      <c r="AF19" s="7"/>
-      <c r="AG19" s="7" t="n">
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1"/>
+      <c r="AG19" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AH19" s="7"/>
-      <c r="AI19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK19" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM19" s="8" t="n">
+      <c r="AH19" s="1"/>
+      <c r="AI19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM19" s="2" t="n">
         <f aca="false">AK19+AL19/2</f>
         <v>7.5</v>
       </c>
-      <c r="AN19" s="11" t="n">
+      <c r="AN19" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(AG19,AI19,AJ19,AM19),0)</f>
         <v>4</v>
       </c>
-      <c r="AO19" s="7" t="n">
+      <c r="AO19" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(T19,AN19),0)</f>
         <v>6</v>
       </c>
-      <c r="AP19" s="8" t="n">
+      <c r="AP19" s="2" t="n">
         <f aca="false">ROUND(AVERAGE(AC19,AG19,AI19,AJ19),0)</f>
         <v>2</v>
       </c>
-      <c r="AQ19" s="11" t="n">
-        <f aca="false">ROUND(AP19*6/10,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AMM19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
+      <c r="AQ19" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR19" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AMM19" s="1"/>
+    </row>
+    <row r="20" s="24" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="24" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="1" t="n">
+      <c r="B20" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="24" t="n">
         <f aca="false">I20+K20/2</f>
         <v>1</v>
       </c>
-      <c r="M20" s="1" t="n">
+      <c r="M20" s="24" t="n">
         <f aca="false">ROUND(AVERAGE(C20,E20,G20,L20),0)</f>
         <v>7</v>
       </c>
-      <c r="N20" s="6" t="str">
+      <c r="N20" s="26" t="str">
         <f aca="false">IF(M20&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="1" t="n">
+      <c r="O20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="24" t="n">
         <v>8.5</v>
       </c>
-      <c r="S20" s="1" t="n">
+      <c r="S20" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="T20" s="26" t="n">
         <f aca="false">ROUND(AVERAGE(S20,Q20,O20,M20),0)</f>
         <v>6</v>
       </c>
-      <c r="V20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK20" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM20" s="2" t="n">
+      <c r="V20" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM20" s="25" t="n">
         <f aca="false">AK20+AL20/2</f>
         <v>7.5</v>
       </c>
-      <c r="AN20" s="6" t="n">
+      <c r="AN20" s="26" t="n">
         <f aca="false">ROUND(AVERAGE(AG20,AI20,AJ20,AM20),0)</f>
         <v>3</v>
       </c>
-      <c r="AO20" s="6" t="n">
+      <c r="AO20" s="26" t="n">
         <f aca="false">ROUND(AVERAGE(T20,AN20),0)</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
+      <c r="AQ20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR20" s="24" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" s="20" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1" t="n">
+      <c r="B21" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="I21" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="L21" s="1" t="n">
+      <c r="L21" s="20" t="n">
         <f aca="false">I21+K21/2</f>
         <v>2.5</v>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="M21" s="20" t="n">
         <f aca="false">ROUND(AVERAGE(C21,E21,G21,L21),0)</f>
         <v>8</v>
       </c>
-      <c r="N21" s="6" t="str">
+      <c r="N21" s="23" t="str">
         <f aca="false">IF(M21&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="1" t="n">
+      <c r="O21" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="20" t="n">
         <v>8.5</v>
       </c>
-      <c r="S21" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T21" s="6" t="n">
+      <c r="S21" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="T21" s="23" t="n">
         <f aca="false">ROUND(AVERAGE(S21,Q21,O21,M21),0)</f>
         <v>7</v>
       </c>
-      <c r="AC21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH21" s="2"/>
-      <c r="AI21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AK21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" s="2" t="n">
+      <c r="AC21" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH21" s="21"/>
+      <c r="AI21" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ21" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="21" t="n">
         <f aca="false">AK21+AL21/2</f>
         <v>0</v>
       </c>
-      <c r="AN21" s="6" t="n">
+      <c r="AN21" s="23" t="n">
         <f aca="false">ROUND(AVERAGE(AG21,AI21,AJ21,AM21),0)</f>
         <v>0</v>
       </c>
-      <c r="AO21" s="6" t="n">
+      <c r="AO21" s="23" t="n">
         <f aca="false">ROUND(AVERAGE(T21,AN21),0)</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AS21" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT21" s="20" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>10</v>
@@ -7101,7 +7344,7 @@
       <c r="G22" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I22" s="17" t="n">
+      <c r="I22" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J22" s="3" t="n">
@@ -7122,10 +7365,10 @@
         <f aca="false">IF(M22&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O22" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="P22" s="13" t="n">
+      <c r="O22" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>45784</v>
       </c>
       <c r="Q22" s="1" t="n">
@@ -7134,7 +7377,7 @@
       <c r="S22" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="T22" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S22,Q22,O22,M22),0)</f>
         <v>9</v>
       </c>
@@ -7169,12 +7412,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>9</v>
@@ -7203,10 +7446,10 @@
         <f aca="false">IF(M23&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O23" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="P23" s="13" t="n">
+      <c r="O23" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="P23" s="3" t="n">
         <v>45782</v>
       </c>
       <c r="Q23" s="1" t="n">
@@ -7215,7 +7458,7 @@
       <c r="S23" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="T23" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S23,Q23,O23,M23),0)</f>
         <v>8</v>
       </c>
@@ -7250,126 +7493,128 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" s="8" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
+    <row r="24" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7" t="n">
+      <c r="B24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7" t="n">
+      <c r="H24" s="1"/>
+      <c r="I24" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7" t="n">
+      <c r="J24" s="1"/>
+      <c r="K24" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="L24" s="1" t="n">
         <f aca="false">I24+K24/2</f>
         <v>7.5</v>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M24" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C24,E24,G24,L24),0)</f>
         <v>9</v>
       </c>
-      <c r="N24" s="11" t="str">
+      <c r="N24" s="6" t="str">
         <f aca="false">IF(M24&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="R24" s="7"/>
-      <c r="S24" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" s="11" t="n">
+      <c r="O24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S24,Q24,O24,M24),0)</f>
         <v>7</v>
       </c>
-      <c r="U24" s="7"/>
-      <c r="V24" s="7"/>
-      <c r="W24" s="7"/>
-      <c r="X24" s="7"/>
-      <c r="Y24" s="7"/>
-      <c r="Z24" s="7"/>
-      <c r="AA24" s="7"/>
-      <c r="AB24" s="7"/>
-      <c r="AC24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD24" s="7"/>
-      <c r="AE24" s="7"/>
-      <c r="AF24" s="7"/>
-      <c r="AG24" s="7" t="n">
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="1"/>
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="1"/>
+      <c r="AG24" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AH24" s="7"/>
-      <c r="AI24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK24" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" s="8" t="n">
+      <c r="AH24" s="1"/>
+      <c r="AI24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK24" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="2" t="n">
         <f aca="false">AK24+AL24/2</f>
         <v>7</v>
       </c>
-      <c r="AN24" s="11" t="n">
+      <c r="AN24" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(AG24,AI24,AJ24,AM24),0)</f>
         <v>3</v>
       </c>
-      <c r="AO24" s="7" t="n">
+      <c r="AO24" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(T24,AN24),0)</f>
         <v>5</v>
       </c>
-      <c r="AP24" s="8" t="n">
+      <c r="AP24" s="2" t="n">
         <f aca="false">ROUND(AVERAGE(AC24,AG24,AI24,AJ24),0)</f>
         <v>2</v>
       </c>
-      <c r="AQ24" s="11" t="n">
-        <f aca="false">ROUND(AP24*6/10,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AMM24" s="7"/>
+      <c r="AQ24" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR24" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AMM24" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="N3:N24">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"TEP"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T3:T24">
-    <cfRule type="cellIs" priority="3" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="cellIs" priority="4" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7403,10 +7648,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ8:AQ24">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>4</formula>
+    <cfRule type="cellIs" priority="13" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="14" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7436,10 +7681,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C1" s="3" t="n">
         <v>45737</v>
@@ -7454,7 +7699,7 @@
         <v>45961</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7462,7 +7707,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>3</v>
@@ -7480,7 +7725,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>0</v>
@@ -7501,7 +7746,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>3</v>
@@ -7516,7 +7761,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>4</v>
@@ -7534,7 +7779,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0</v>
@@ -7552,7 +7797,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>0</v>
@@ -7570,7 +7815,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>3</v>
@@ -7588,7 +7833,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>4</v>
@@ -7609,7 +7854,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>3</v>
@@ -7624,7 +7869,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>3</v>
@@ -7639,7 +7884,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>3</v>
@@ -7660,7 +7905,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>0</v>
@@ -7675,7 +7920,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>3</v>
@@ -7696,7 +7941,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>3</v>
@@ -7717,7 +7962,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>3</v>
@@ -7735,7 +7980,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>0</v>
@@ -7750,7 +7995,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>3</v>
@@ -7768,7 +8013,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>0</v>
@@ -7786,7 +8031,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>3</v>
@@ -7801,7 +8046,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>3</v>
@@ -7819,7 +8064,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>3</v>
@@ -7837,7 +8082,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>3</v>
@@ -7873,25 +8118,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7899,16 +8144,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -7922,16 +8167,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>10</v>
@@ -7945,16 +8190,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -7968,16 +8213,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -7991,7 +8236,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -8005,7 +8250,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -8019,16 +8264,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -8042,16 +8287,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -8070,13 +8315,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8</v>
@@ -8087,16 +8332,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>10</v>
@@ -8110,7 +8355,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>1</v>
@@ -8124,16 +8369,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -8147,16 +8392,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>7</v>
@@ -8170,16 +8415,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -8193,16 +8438,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -8216,16 +8461,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>10</v>
@@ -8239,7 +8484,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>1</v>
@@ -8253,16 +8498,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>10</v>
@@ -8276,16 +8521,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -8299,16 +8544,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -8322,16 +8567,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>10</v>
@@ -8345,16 +8590,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -8373,13 +8618,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -8387,13 +8632,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>7</v>
@@ -8404,16 +8649,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -8449,27 +8694,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>9</v>
@@ -8501,25 +8746,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8527,16 +8772,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -8550,16 +8795,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>10</v>
@@ -8573,16 +8818,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -8596,16 +8841,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -8619,7 +8864,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -8633,7 +8878,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -8647,16 +8892,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -8670,16 +8915,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -8693,16 +8938,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -8716,7 +8961,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -8730,16 +8975,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>10</v>
@@ -8753,16 +8998,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -8776,7 +9021,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>1</v>
@@ -8790,16 +9035,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -8813,16 +9058,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>10</v>
@@ -8836,7 +9081,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -8850,16 +9095,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -8873,16 +9118,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>10</v>
@@ -8896,16 +9141,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>10</v>
@@ -8919,16 +9164,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -8942,16 +9187,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>10</v>
@@ -8970,13 +9215,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -8984,13 +9229,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>8</v>
@@ -8998,13 +9243,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>6</v>
@@ -9012,13 +9257,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>5</v>
@@ -9029,16 +9274,16 @@
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -9073,16 +9318,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9090,16 +9335,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>7</v>
@@ -9110,16 +9355,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>10</v>
@@ -9130,16 +9375,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -9150,16 +9395,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -9170,7 +9415,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -9181,7 +9426,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -9192,16 +9437,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -9212,16 +9457,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -9232,16 +9477,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8</v>
@@ -9252,7 +9497,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -9263,16 +9508,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>10</v>
@@ -9283,16 +9528,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -9303,16 +9548,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>7</v>
@@ -9323,16 +9568,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>7</v>
@@ -9343,16 +9588,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>7</v>
@@ -9363,7 +9608,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -9374,16 +9619,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>8</v>
@@ -9394,16 +9639,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>7</v>
@@ -9414,16 +9659,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -9434,16 +9679,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -9454,16 +9699,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -9474,16 +9719,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>8</v>
@@ -9515,25 +9760,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9541,7 +9786,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -9552,16 +9797,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>9</v>
@@ -9572,7 +9817,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -9583,16 +9828,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>9</v>
@@ -9603,7 +9848,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -9614,7 +9859,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -9625,16 +9870,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -9645,16 +9890,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -9665,16 +9910,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -9685,7 +9930,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -9696,16 +9941,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>7</v>
@@ -9716,16 +9961,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>7</v>
@@ -9736,7 +9981,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>1</v>
@@ -9747,16 +9992,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>7</v>
@@ -9767,16 +10012,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -9787,7 +10032,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -9798,7 +10043,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>1</v>
@@ -9809,7 +10054,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>1</v>
@@ -9820,16 +10065,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>1</v>
@@ -9840,7 +10085,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>1</v>
@@ -9851,16 +10096,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>10</v>
@@ -9868,13 +10113,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>6</v>
@@ -9885,7 +10130,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>1</v>
@@ -9922,36 +10167,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>7</v>
@@ -9962,13 +10207,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>9</v>
@@ -9979,13 +10224,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>6</v>
@@ -10004,13 +10249,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>5</v>
@@ -10018,13 +10263,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>5</v>
@@ -10032,13 +10277,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>5</v>
@@ -10046,13 +10291,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>5</v>
@@ -10060,13 +10305,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>4</v>
@@ -10074,13 +10319,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>3</v>
@@ -10088,13 +10333,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>7</v>
@@ -10105,13 +10350,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>6</v>
@@ -10122,13 +10367,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>5</v>
